--- a/L1/data/bracketology/espn_bracketology_2026.xlsx
+++ b/L1/data/bracketology/espn_bracketology_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ryanbrowder/Documents/Projects/marchMadness/L1/data/bracketology/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F47DA282-F384-2045-B483-37516AE08CC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81C426D6-FB17-C447-AA7C-65DDA723ACBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16180" yWindow="900" windowWidth="12720" windowHeight="17180" xr2:uid="{F87E21A2-B3CC-9145-B55E-990F91045160}"/>
+    <workbookView xWindow="14700" yWindow="780" windowWidth="14180" windowHeight="17180" activeTab="1" xr2:uid="{F87E21A2-B3CC-9145-B55E-990F91045160}"/>
   </bookViews>
   <sheets>
     <sheet name="espn_bracketology_2026" sheetId="1" r:id="rId1"/>
@@ -5214,11 +5214,11 @@
         <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>11</v>
+        <v>944</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
-        <v>104</v>
+        <v>330</v>
       </c>
       <c r="G10" t="s">
         <v>23</v>
@@ -5235,11 +5235,11 @@
         <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>944</v>
+        <v>900</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
-        <v>330</v>
+        <v>313</v>
       </c>
       <c r="G11" t="s">
         <v>78</v>
@@ -5256,11 +5256,11 @@
         <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>548</v>
+        <v>519</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="G12" t="s">
         <v>79</v>
@@ -5277,11 +5277,11 @@
         <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="D13">
         <f t="shared" si="0"/>
-        <v>150</v>
+        <v>380</v>
       </c>
       <c r="G13" t="s">
         <v>80</v>
@@ -5298,11 +5298,11 @@
         <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>634</v>
+        <v>16</v>
       </c>
       <c r="D14">
         <f t="shared" si="0"/>
-        <v>215</v>
+        <v>337</v>
       </c>
       <c r="G14" t="s">
         <v>81</v>
@@ -5340,11 +5340,11 @@
         <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>990</v>
+        <v>1052</v>
       </c>
       <c r="D16">
         <f t="shared" si="0"/>
-        <v>348</v>
+        <v>377</v>
       </c>
       <c r="G16" t="s">
         <v>83</v>
@@ -5361,11 +5361,11 @@
         <v>16</v>
       </c>
       <c r="C17" t="s">
-        <v>95</v>
+        <v>432</v>
       </c>
       <c r="D17">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>143</v>
       </c>
       <c r="G17" t="s">
         <v>84</v>
@@ -5424,11 +5424,11 @@
         <v>3</v>
       </c>
       <c r="C20" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="D20">
         <f t="shared" si="0"/>
-        <v>91</v>
+        <v>199</v>
       </c>
       <c r="G20" t="s">
         <v>87</v>
@@ -5466,11 +5466,11 @@
         <v>5</v>
       </c>
       <c r="C22" t="s">
-        <v>6</v>
+        <v>59</v>
       </c>
       <c r="D22">
         <f t="shared" si="0"/>
-        <v>353</v>
+        <v>13</v>
       </c>
       <c r="G22" t="s">
         <v>89</v>
@@ -5508,11 +5508,11 @@
         <v>7</v>
       </c>
       <c r="C24" t="s">
-        <v>65</v>
+        <v>12</v>
       </c>
       <c r="D24">
         <f t="shared" si="0"/>
-        <v>355</v>
+        <v>374</v>
       </c>
       <c r="G24" t="s">
         <v>91</v>
@@ -5529,11 +5529,11 @@
         <v>8</v>
       </c>
       <c r="C25" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D25">
         <f t="shared" si="0"/>
-        <v>260</v>
+        <v>177</v>
       </c>
       <c r="G25" t="s">
         <v>92</v>
@@ -5550,11 +5550,11 @@
         <v>9</v>
       </c>
       <c r="C26" t="s">
-        <v>899</v>
+        <v>11</v>
       </c>
       <c r="D26">
         <f t="shared" si="0"/>
-        <v>313</v>
+        <v>104</v>
       </c>
       <c r="G26" t="s">
         <v>93</v>
@@ -5571,11 +5571,11 @@
         <v>10</v>
       </c>
       <c r="C27" t="s">
-        <v>45</v>
+        <v>548</v>
       </c>
       <c r="D27">
         <f t="shared" si="0"/>
-        <v>331</v>
+        <v>187</v>
       </c>
       <c r="G27" t="s">
         <v>94</v>
@@ -5592,11 +5592,11 @@
         <v>11</v>
       </c>
       <c r="C28" t="s">
-        <v>878</v>
+        <v>43</v>
       </c>
       <c r="D28">
         <f t="shared" si="0"/>
-        <v>304</v>
+        <v>17</v>
       </c>
       <c r="G28" t="s">
         <v>95</v>
@@ -5613,11 +5613,11 @@
         <v>12</v>
       </c>
       <c r="C29" t="s">
-        <v>15</v>
+        <v>826</v>
       </c>
       <c r="D29">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>284</v>
       </c>
       <c r="G29" t="s">
         <v>96</v>
@@ -5634,11 +5634,11 @@
         <v>13</v>
       </c>
       <c r="C30" t="s">
-        <v>868</v>
+        <v>66</v>
       </c>
       <c r="D30">
         <f t="shared" si="0"/>
-        <v>299</v>
+        <v>116</v>
       </c>
       <c r="G30" t="s">
         <v>97</v>
@@ -5655,11 +5655,11 @@
         <v>14</v>
       </c>
       <c r="C31" t="s">
-        <v>269</v>
+        <v>589</v>
       </c>
       <c r="D31">
         <f t="shared" si="0"/>
-        <v>79</v>
+        <v>198</v>
       </c>
       <c r="G31" t="s">
         <v>98</v>
@@ -5676,11 +5676,11 @@
         <v>15</v>
       </c>
       <c r="C32" t="s">
-        <v>1052</v>
+        <v>705</v>
       </c>
       <c r="D32">
         <f t="shared" si="0"/>
-        <v>377</v>
+        <v>243</v>
       </c>
       <c r="G32" t="s">
         <v>99</v>
@@ -5697,11 +5697,11 @@
         <v>16</v>
       </c>
       <c r="C33" t="s">
-        <v>830</v>
+        <v>570</v>
       </c>
       <c r="D33">
         <f t="shared" si="0"/>
-        <v>286</v>
+        <v>193</v>
       </c>
       <c r="G33" t="s">
         <v>54</v>
@@ -5739,11 +5739,11 @@
         <v>2</v>
       </c>
       <c r="C35" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D35">
         <f t="shared" si="0"/>
-        <v>119</v>
+        <v>91</v>
       </c>
       <c r="G35" t="s">
         <v>101</v>
@@ -5760,11 +5760,11 @@
         <v>3</v>
       </c>
       <c r="C36" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="D36">
         <f t="shared" si="0"/>
-        <v>199</v>
+        <v>119</v>
       </c>
       <c r="G36" t="s">
         <v>102</v>
@@ -5802,11 +5802,11 @@
         <v>5</v>
       </c>
       <c r="C38" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="D38">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>308</v>
       </c>
       <c r="G38" t="s">
         <v>104</v>
@@ -5823,11 +5823,11 @@
         <v>6</v>
       </c>
       <c r="C39" t="s">
-        <v>764</v>
+        <v>65</v>
       </c>
       <c r="D39">
         <f t="shared" si="0"/>
-        <v>265</v>
+        <v>355</v>
       </c>
       <c r="G39" t="s">
         <v>59</v>
@@ -5844,11 +5844,11 @@
         <v>7</v>
       </c>
       <c r="C40" t="s">
-        <v>12</v>
+        <v>764</v>
       </c>
       <c r="D40">
         <f t="shared" si="0"/>
-        <v>374</v>
+        <v>265</v>
       </c>
       <c r="G40" t="s">
         <v>105</v>
@@ -5865,11 +5865,11 @@
         <v>8</v>
       </c>
       <c r="C41" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="D41">
         <f t="shared" si="0"/>
-        <v>142</v>
+        <v>196</v>
       </c>
       <c r="G41" t="s">
         <v>106</v>
@@ -5886,11 +5886,11 @@
         <v>9</v>
       </c>
       <c r="C42" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="D42">
         <f t="shared" si="0"/>
-        <v>55</v>
+        <v>331</v>
       </c>
       <c r="G42" t="s">
         <v>107</v>
@@ -5928,11 +5928,11 @@
         <v>11</v>
       </c>
       <c r="C44" t="s">
-        <v>519</v>
+        <v>799</v>
       </c>
       <c r="D44">
         <f t="shared" si="0"/>
-        <v>178</v>
+        <v>274</v>
       </c>
       <c r="G44" t="s">
         <v>109</v>
@@ -5949,11 +5949,11 @@
         <v>12</v>
       </c>
       <c r="C45" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="D45">
         <f t="shared" si="0"/>
-        <v>380</v>
+        <v>150</v>
       </c>
       <c r="G45" t="s">
         <v>110</v>
@@ -5970,11 +5970,11 @@
         <v>13</v>
       </c>
       <c r="C46" t="s">
-        <v>16</v>
+        <v>634</v>
       </c>
       <c r="D46">
         <f t="shared" si="0"/>
-        <v>337</v>
+        <v>215</v>
       </c>
       <c r="G46" t="s">
         <v>111</v>
@@ -5991,11 +5991,11 @@
         <v>14</v>
       </c>
       <c r="C47" t="s">
-        <v>589</v>
+        <v>269</v>
       </c>
       <c r="D47">
         <f t="shared" si="0"/>
-        <v>198</v>
+        <v>79</v>
       </c>
       <c r="G47" t="s">
         <v>17</v>
@@ -6012,11 +6012,11 @@
         <v>15</v>
       </c>
       <c r="C48" t="s">
-        <v>705</v>
+        <v>490</v>
       </c>
       <c r="D48">
         <f t="shared" si="0"/>
-        <v>243</v>
+        <v>167</v>
       </c>
       <c r="G48" t="s">
         <v>112</v>
@@ -6138,11 +6138,11 @@
         <v>5</v>
       </c>
       <c r="C54" t="s">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="D54">
         <f t="shared" si="0"/>
-        <v>308</v>
+        <v>353</v>
       </c>
       <c r="G54" t="s">
         <v>39</v>
@@ -6180,11 +6180,11 @@
         <v>7</v>
       </c>
       <c r="C56" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="D56">
         <f t="shared" si="0"/>
-        <v>196</v>
+        <v>142</v>
       </c>
       <c r="G56" t="s">
         <v>118</v>
@@ -6201,11 +6201,11 @@
         <v>8</v>
       </c>
       <c r="C57" t="s">
-        <v>62</v>
+        <v>768</v>
       </c>
       <c r="D57">
         <f t="shared" si="0"/>
-        <v>177</v>
+        <v>266</v>
       </c>
       <c r="G57" t="s">
         <v>119</v>
@@ -6222,11 +6222,11 @@
         <v>9</v>
       </c>
       <c r="C58" t="s">
-        <v>768</v>
+        <v>28</v>
       </c>
       <c r="D58">
         <f t="shared" si="0"/>
-        <v>266</v>
+        <v>55</v>
       </c>
       <c r="G58" t="s">
         <v>120</v>
@@ -6243,11 +6243,11 @@
         <v>10</v>
       </c>
       <c r="C59" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="D59">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>260</v>
       </c>
       <c r="G59" t="s">
         <v>121</v>
@@ -6264,11 +6264,11 @@
         <v>11</v>
       </c>
       <c r="C60" t="s">
-        <v>61</v>
+        <v>787</v>
       </c>
       <c r="D60">
         <f t="shared" si="0"/>
-        <v>129</v>
+        <v>271</v>
       </c>
       <c r="G60" t="s">
         <v>122</v>
@@ -6285,11 +6285,11 @@
         <v>12</v>
       </c>
       <c r="C61" t="s">
-        <v>826</v>
+        <v>15</v>
       </c>
       <c r="D61">
         <f t="shared" si="0"/>
-        <v>284</v>
+        <v>23</v>
       </c>
       <c r="G61" t="s">
         <v>13</v>
@@ -6306,11 +6306,11 @@
         <v>13</v>
       </c>
       <c r="C62" t="s">
-        <v>66</v>
+        <v>868</v>
       </c>
       <c r="D62">
         <f t="shared" si="0"/>
-        <v>116</v>
+        <v>299</v>
       </c>
       <c r="G62" t="s">
         <v>1065</v>
@@ -6369,11 +6369,11 @@
         <v>16</v>
       </c>
       <c r="C65" t="s">
-        <v>432</v>
+        <v>990</v>
       </c>
       <c r="D65">
         <f t="shared" si="0"/>
-        <v>143</v>
+        <v>348</v>
       </c>
       <c r="G65" t="s">
         <v>125</v>

--- a/L1/data/bracketology/espn_bracketology_2026.xlsx
+++ b/L1/data/bracketology/espn_bracketology_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ryanbrowder/Documents/Projects/marchMadness/L1/data/bracketology/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81C426D6-FB17-C447-AA7C-65DDA723ACBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04327F0B-DC9B-2545-87C8-CE1011EFB3F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14700" yWindow="780" windowWidth="14180" windowHeight="17180" activeTab="1" xr2:uid="{F87E21A2-B3CC-9145-B55E-990F91045160}"/>
+    <workbookView xWindow="11820" yWindow="780" windowWidth="17060" windowHeight="17180" xr2:uid="{F87E21A2-B3CC-9145-B55E-990F91045160}"/>
   </bookViews>
   <sheets>
     <sheet name="espn_bracketology_2026" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1476" uniqueCount="1067">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1492" uniqueCount="1067">
   <si>
     <t>Region</t>
   </si>
@@ -4095,7 +4095,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69C429B0-D6C8-FD4E-9C9D-EB00E293E02D}">
-  <dimension ref="A1:D65"/>
+  <dimension ref="A1:D69"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
@@ -4134,10 +4134,10 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>55</v>
+        <v>522</v>
       </c>
       <c r="D3">
-        <v>248</v>
+        <v>180</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -4148,10 +4148,10 @@
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="D4">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -4162,10 +4162,10 @@
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -4176,10 +4176,10 @@
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>857</v>
+        <v>25</v>
       </c>
       <c r="D6">
-        <v>296</v>
+        <v>308</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -4204,10 +4204,10 @@
         <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>986</v>
+        <v>65</v>
       </c>
       <c r="D8">
-        <v>347</v>
+        <v>355</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -4218,10 +4218,10 @@
         <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>10</v>
+        <v>764</v>
       </c>
       <c r="D9">
-        <v>132</v>
+        <v>265</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -4232,10 +4232,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D10">
-        <v>104</v>
+        <v>132</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
@@ -4246,10 +4246,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>944</v>
+        <v>878</v>
       </c>
       <c r="D11">
-        <v>330</v>
+        <v>304</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
@@ -4260,10 +4260,10 @@
         <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>548</v>
+        <v>799</v>
       </c>
       <c r="D12">
-        <v>187</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
@@ -4271,13 +4271,13 @@
         <v>3</v>
       </c>
       <c r="B13">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D13">
-        <v>150</v>
+        <v>229</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
@@ -4285,13 +4285,13 @@
         <v>3</v>
       </c>
       <c r="B14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>634</v>
+        <v>31</v>
       </c>
       <c r="D14">
-        <v>215</v>
+        <v>380</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
@@ -4299,13 +4299,13 @@
         <v>3</v>
       </c>
       <c r="B15">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>116</v>
+        <v>16</v>
       </c>
       <c r="D15">
-        <v>18</v>
+        <v>337</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
@@ -4313,13 +4313,13 @@
         <v>3</v>
       </c>
       <c r="B16">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>990</v>
+        <v>634</v>
       </c>
       <c r="D16">
-        <v>348</v>
+        <v>215</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
@@ -4327,27 +4327,27 @@
         <v>3</v>
       </c>
       <c r="B17">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>95</v>
+        <v>1052</v>
       </c>
       <c r="D17">
-        <v>10</v>
+        <v>377</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>21</v>
+        <v>186</v>
       </c>
       <c r="D18">
-        <v>179</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
@@ -4355,13 +4355,13 @@
         <v>20</v>
       </c>
       <c r="B19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>401</v>
+        <v>21</v>
       </c>
       <c r="D19">
-        <v>133</v>
+        <v>179</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
@@ -4369,13 +4369,13 @@
         <v>20</v>
       </c>
       <c r="B20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C20" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D20">
-        <v>91</v>
+        <v>119</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
@@ -4383,13 +4383,13 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C21" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D21">
-        <v>356</v>
+        <v>199</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
@@ -4397,13 +4397,13 @@
         <v>20</v>
       </c>
       <c r="B22">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C22" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="D22">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
@@ -4411,13 +4411,13 @@
         <v>20</v>
       </c>
       <c r="B23">
+        <v>5</v>
+      </c>
+      <c r="C23" t="s">
         <v>6</v>
       </c>
-      <c r="C23" t="s">
-        <v>57</v>
-      </c>
       <c r="D23">
-        <v>211</v>
+        <v>353</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
@@ -4425,13 +4425,13 @@
         <v>20</v>
       </c>
       <c r="B24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C24" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="D24">
-        <v>355</v>
+        <v>211</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
@@ -4439,13 +4439,13 @@
         <v>20</v>
       </c>
       <c r="B25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C25" t="s">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="D25">
-        <v>260</v>
+        <v>374</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
@@ -4453,13 +4453,13 @@
         <v>20</v>
       </c>
       <c r="B26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C26" t="s">
-        <v>899</v>
+        <v>944</v>
       </c>
       <c r="D26">
-        <v>313</v>
+        <v>330</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
@@ -4467,13 +4467,13 @@
         <v>20</v>
       </c>
       <c r="B27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C27" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D27">
-        <v>331</v>
+        <v>196</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
@@ -4481,13 +4481,13 @@
         <v>20</v>
       </c>
       <c r="B28">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C28" t="s">
-        <v>878</v>
+        <v>897</v>
       </c>
       <c r="D28">
-        <v>304</v>
+        <v>312</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
@@ -4495,13 +4495,13 @@
         <v>20</v>
       </c>
       <c r="B29">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C29" t="s">
-        <v>15</v>
+        <v>602</v>
       </c>
       <c r="D29">
-        <v>23</v>
+        <v>204</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
@@ -4509,13 +4509,13 @@
         <v>20</v>
       </c>
       <c r="B30">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C30" t="s">
-        <v>868</v>
+        <v>61</v>
       </c>
       <c r="D30">
-        <v>299</v>
+        <v>129</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
@@ -4523,13 +4523,13 @@
         <v>20</v>
       </c>
       <c r="B31">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C31" t="s">
-        <v>269</v>
+        <v>50</v>
       </c>
       <c r="D31">
-        <v>79</v>
+        <v>150</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
@@ -4537,13 +4537,13 @@
         <v>20</v>
       </c>
       <c r="B32">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C32" t="s">
-        <v>1052</v>
+        <v>156</v>
       </c>
       <c r="D32">
-        <v>377</v>
+        <v>36</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
@@ -4551,55 +4551,55 @@
         <v>20</v>
       </c>
       <c r="B33">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C33" t="s">
-        <v>830</v>
+        <v>934</v>
       </c>
       <c r="D33">
-        <v>286</v>
+        <v>326</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B34">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C34" t="s">
-        <v>1064</v>
+        <v>705</v>
       </c>
       <c r="D34">
-        <v>62</v>
+        <v>243</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B35">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C35" t="s">
-        <v>56</v>
+        <v>372</v>
       </c>
       <c r="D35">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B36">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C36" t="s">
-        <v>27</v>
+        <v>126</v>
       </c>
       <c r="D36">
-        <v>199</v>
+        <v>24</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
@@ -4607,13 +4607,13 @@
         <v>37</v>
       </c>
       <c r="B37">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C37" t="s">
-        <v>8</v>
+        <v>1064</v>
       </c>
       <c r="D37">
-        <v>317</v>
+        <v>62</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
@@ -4621,13 +4621,13 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C38" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D38">
-        <v>13</v>
+        <v>91</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
@@ -4635,13 +4635,13 @@
         <v>37</v>
       </c>
       <c r="B39">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C39" t="s">
-        <v>764</v>
+        <v>55</v>
       </c>
       <c r="D39">
-        <v>265</v>
+        <v>248</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
@@ -4649,13 +4649,13 @@
         <v>37</v>
       </c>
       <c r="B40">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C40" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D40">
-        <v>374</v>
+        <v>317</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
@@ -4663,13 +4663,13 @@
         <v>37</v>
       </c>
       <c r="B41">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C41" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="D41">
-        <v>142</v>
+        <v>13</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
@@ -4677,13 +4677,13 @@
         <v>37</v>
       </c>
       <c r="B42">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C42" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D42">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
@@ -4691,13 +4691,13 @@
         <v>37</v>
       </c>
       <c r="B43">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C43" t="s">
-        <v>897</v>
+        <v>29</v>
       </c>
       <c r="D43">
-        <v>312</v>
+        <v>347</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
@@ -4705,13 +4705,13 @@
         <v>37</v>
       </c>
       <c r="B44">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C44" t="s">
-        <v>519</v>
+        <v>62</v>
       </c>
       <c r="D44">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
@@ -4719,13 +4719,13 @@
         <v>37</v>
       </c>
       <c r="B45">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C45" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="D45">
-        <v>380</v>
+        <v>104</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
@@ -4733,13 +4733,13 @@
         <v>37</v>
       </c>
       <c r="B46">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C46" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="D46">
-        <v>337</v>
+        <v>331</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
@@ -4747,13 +4747,13 @@
         <v>37</v>
       </c>
       <c r="B47">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C47" t="s">
-        <v>589</v>
+        <v>899</v>
       </c>
       <c r="D47">
-        <v>198</v>
+        <v>313</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
@@ -4761,13 +4761,13 @@
         <v>37</v>
       </c>
       <c r="B48">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C48" t="s">
-        <v>705</v>
+        <v>826</v>
       </c>
       <c r="D48">
-        <v>243</v>
+        <v>284</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
@@ -4775,69 +4775,69 @@
         <v>37</v>
       </c>
       <c r="B49">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C49" t="s">
-        <v>945</v>
+        <v>868</v>
       </c>
       <c r="D49">
-        <v>332</v>
+        <v>299</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="B50">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C50" t="s">
-        <v>54</v>
+        <v>926</v>
       </c>
       <c r="D50">
-        <v>11</v>
+        <v>321</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="B51">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C51" t="s">
-        <v>7</v>
+        <v>513</v>
       </c>
       <c r="D51">
-        <v>125</v>
+        <v>176</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="B52">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C52" t="s">
-        <v>22</v>
+        <v>432</v>
       </c>
       <c r="D52">
-        <v>108</v>
+        <v>143</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="B53">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C53" t="s">
-        <v>522</v>
+        <v>945</v>
       </c>
       <c r="D53">
-        <v>180</v>
+        <v>332</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
@@ -4845,13 +4845,13 @@
         <v>53</v>
       </c>
       <c r="B54">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C54" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="D54">
-        <v>308</v>
+        <v>11</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
@@ -4859,13 +4859,13 @@
         <v>53</v>
       </c>
       <c r="B55">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C55" t="s">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="D55">
-        <v>19</v>
+        <v>125</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
@@ -4873,13 +4873,13 @@
         <v>53</v>
       </c>
       <c r="B56">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C56" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D56">
-        <v>196</v>
+        <v>138</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
@@ -4887,13 +4887,13 @@
         <v>53</v>
       </c>
       <c r="B57">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C57" t="s">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="D57">
-        <v>177</v>
+        <v>4</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
@@ -4901,13 +4901,13 @@
         <v>53</v>
       </c>
       <c r="B58">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C58" t="s">
-        <v>768</v>
+        <v>857</v>
       </c>
       <c r="D58">
-        <v>266</v>
+        <v>296</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
@@ -4915,13 +4915,13 @@
         <v>53</v>
       </c>
       <c r="B59">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C59" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D59">
-        <v>17</v>
+        <v>142</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
@@ -4929,13 +4929,13 @@
         <v>53</v>
       </c>
       <c r="B60">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C60" t="s">
-        <v>61</v>
+        <v>768</v>
       </c>
       <c r="D60">
-        <v>129</v>
+        <v>266</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
@@ -4943,13 +4943,13 @@
         <v>53</v>
       </c>
       <c r="B61">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C61" t="s">
-        <v>826</v>
+        <v>28</v>
       </c>
       <c r="D61">
-        <v>284</v>
+        <v>55</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
@@ -4957,13 +4957,13 @@
         <v>53</v>
       </c>
       <c r="B62">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C62" t="s">
-        <v>66</v>
+        <v>548</v>
       </c>
       <c r="D62">
-        <v>116</v>
+        <v>187</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
@@ -4971,13 +4971,13 @@
         <v>53</v>
       </c>
       <c r="B63">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C63" t="s">
-        <v>934</v>
+        <v>60</v>
       </c>
       <c r="D63">
-        <v>326</v>
+        <v>260</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
@@ -4985,13 +4985,13 @@
         <v>53</v>
       </c>
       <c r="B64">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C64" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="D64">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
@@ -4999,13 +4999,69 @@
         <v>53</v>
       </c>
       <c r="B65">
+        <v>12</v>
+      </c>
+      <c r="C65" t="s">
+        <v>15</v>
+      </c>
+      <c r="D65">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>53</v>
+      </c>
+      <c r="B66">
+        <v>13</v>
+      </c>
+      <c r="C66" t="s">
+        <v>66</v>
+      </c>
+      <c r="D66">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>53</v>
+      </c>
+      <c r="B67">
+        <v>14</v>
+      </c>
+      <c r="C67" t="s">
+        <v>589</v>
+      </c>
+      <c r="D67">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>53</v>
+      </c>
+      <c r="B68">
+        <v>15</v>
+      </c>
+      <c r="C68" t="s">
+        <v>269</v>
+      </c>
+      <c r="D68">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>53</v>
+      </c>
+      <c r="B69">
         <v>16</v>
       </c>
-      <c r="C65" t="s">
-        <v>432</v>
-      </c>
-      <c r="D65">
-        <v>143</v>
+      <c r="C69" t="s">
+        <v>893</v>
+      </c>
+      <c r="D69">
+        <v>310</v>
       </c>
     </row>
   </sheetData>
@@ -5067,11 +5123,11 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>55</v>
+        <v>522</v>
       </c>
       <c r="D3">
         <f t="shared" ref="D3:D65" si="0">VLOOKUP(C3,$G$2:$H$1211,2,FALSE)</f>
-        <v>248</v>
+        <v>180</v>
       </c>
       <c r="G3" t="s">
         <v>72</v>
@@ -5088,11 +5144,11 @@
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="G4" t="s">
         <v>73</v>
@@ -5109,11 +5165,11 @@
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>108</v>
       </c>
       <c r="G5" t="s">
         <v>74</v>
@@ -5130,11 +5186,11 @@
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>857</v>
+        <v>25</v>
       </c>
       <c r="D6">
         <f t="shared" si="0"/>
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="G6" t="s">
         <v>75</v>
@@ -5172,11 +5228,11 @@
         <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>986</v>
+        <v>65</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="G8" t="s">
         <v>64</v>
@@ -5193,11 +5249,11 @@
         <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>10</v>
+        <v>764</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
-        <v>132</v>
+        <v>265</v>
       </c>
       <c r="G9" t="s">
         <v>77</v>
@@ -5214,11 +5270,11 @@
         <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>944</v>
+        <v>10</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
-        <v>330</v>
+        <v>132</v>
       </c>
       <c r="G10" t="s">
         <v>23</v>
@@ -5235,11 +5291,11 @@
         <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>900</v>
+        <v>878</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="G11" t="s">
         <v>78</v>
@@ -5256,11 +5312,11 @@
         <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>519</v>
+        <v>799</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
-        <v>178</v>
+        <v>274</v>
       </c>
       <c r="G12" t="s">
         <v>79</v>
@@ -5274,14 +5330,14 @@
         <v>3</v>
       </c>
       <c r="B13">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="D13">
         <f t="shared" si="0"/>
-        <v>380</v>
+        <v>229</v>
       </c>
       <c r="G13" t="s">
         <v>80</v>
@@ -5295,14 +5351,14 @@
         <v>3</v>
       </c>
       <c r="B14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="D14">
-        <f t="shared" si="0"/>
-        <v>337</v>
+        <f>VLOOKUP(C14,$G$2:$H$1211,2,FALSE)</f>
+        <v>380</v>
       </c>
       <c r="G14" t="s">
         <v>81</v>
@@ -5316,14 +5372,14 @@
         <v>3</v>
       </c>
       <c r="B15">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>116</v>
+        <v>16</v>
       </c>
       <c r="D15">
-        <f t="shared" si="0"/>
-        <v>18</v>
+        <f>VLOOKUP(C15,$G$2:$H$1211,2,FALSE)</f>
+        <v>337</v>
       </c>
       <c r="G15" t="s">
         <v>82</v>
@@ -5337,14 +5393,14 @@
         <v>3</v>
       </c>
       <c r="B16">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>1052</v>
+        <v>634</v>
       </c>
       <c r="D16">
-        <f t="shared" si="0"/>
-        <v>377</v>
+        <f>VLOOKUP(C16,$G$2:$H$1211,2,FALSE)</f>
+        <v>215</v>
       </c>
       <c r="G16" t="s">
         <v>83</v>
@@ -5358,14 +5414,14 @@
         <v>3</v>
       </c>
       <c r="B17">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>432</v>
+        <v>1052</v>
       </c>
       <c r="D17">
-        <f t="shared" si="0"/>
-        <v>143</v>
+        <f>VLOOKUP(C17,$G$2:$H$1211,2,FALSE)</f>
+        <v>377</v>
       </c>
       <c r="G17" t="s">
         <v>84</v>
@@ -5376,17 +5432,17 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>21</v>
+        <v>186</v>
       </c>
       <c r="D18">
-        <f t="shared" si="0"/>
-        <v>179</v>
+        <f>VLOOKUP(C18,$G$2:$H$1211,2,FALSE)</f>
+        <v>45</v>
       </c>
       <c r="G18" t="s">
         <v>85</v>
@@ -5400,14 +5456,14 @@
         <v>20</v>
       </c>
       <c r="B19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>401</v>
+        <v>21</v>
       </c>
       <c r="D19">
-        <f t="shared" si="0"/>
-        <v>133</v>
+        <f>VLOOKUP(C19,$G$2:$H$1211,2,FALSE)</f>
+        <v>179</v>
       </c>
       <c r="G19" t="s">
         <v>86</v>
@@ -5421,14 +5477,14 @@
         <v>20</v>
       </c>
       <c r="B20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C20" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="D20">
-        <f t="shared" si="0"/>
-        <v>199</v>
+        <f>VLOOKUP(C20,$G$2:$H$1211,2,FALSE)</f>
+        <v>119</v>
       </c>
       <c r="G20" t="s">
         <v>87</v>
@@ -5442,14 +5498,14 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C21" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D21">
-        <f t="shared" si="0"/>
-        <v>356</v>
+        <f>VLOOKUP(C21,$G$2:$H$1211,2,FALSE)</f>
+        <v>199</v>
       </c>
       <c r="G21" t="s">
         <v>88</v>
@@ -5463,14 +5519,14 @@
         <v>20</v>
       </c>
       <c r="B22">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C22" t="s">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="D22">
-        <f t="shared" si="0"/>
-        <v>13</v>
+        <f>VLOOKUP(C22,$G$2:$H$1211,2,FALSE)</f>
+        <v>356</v>
       </c>
       <c r="G22" t="s">
         <v>89</v>
@@ -5484,14 +5540,14 @@
         <v>20</v>
       </c>
       <c r="B23">
+        <v>5</v>
+      </c>
+      <c r="C23" t="s">
         <v>6</v>
       </c>
-      <c r="C23" t="s">
-        <v>57</v>
-      </c>
       <c r="D23">
-        <f t="shared" si="0"/>
-        <v>211</v>
+        <f>VLOOKUP(C23,$G$2:$H$1211,2,FALSE)</f>
+        <v>353</v>
       </c>
       <c r="G23" t="s">
         <v>90</v>
@@ -5505,14 +5561,14 @@
         <v>20</v>
       </c>
       <c r="B24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C24" t="s">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="D24">
-        <f t="shared" si="0"/>
-        <v>374</v>
+        <f>VLOOKUP(C24,$G$2:$H$1211,2,FALSE)</f>
+        <v>211</v>
       </c>
       <c r="G24" t="s">
         <v>91</v>
@@ -5526,14 +5582,14 @@
         <v>20</v>
       </c>
       <c r="B25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C25" t="s">
-        <v>62</v>
+        <v>12</v>
       </c>
       <c r="D25">
-        <f t="shared" si="0"/>
-        <v>177</v>
+        <f>VLOOKUP(C25,$G$2:$H$1211,2,FALSE)</f>
+        <v>374</v>
       </c>
       <c r="G25" t="s">
         <v>92</v>
@@ -5547,14 +5603,14 @@
         <v>20</v>
       </c>
       <c r="B26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C26" t="s">
-        <v>11</v>
+        <v>944</v>
       </c>
       <c r="D26">
-        <f t="shared" si="0"/>
-        <v>104</v>
+        <f>VLOOKUP(C26,$G$2:$H$1211,2,FALSE)</f>
+        <v>330</v>
       </c>
       <c r="G26" t="s">
         <v>93</v>
@@ -5568,14 +5624,14 @@
         <v>20</v>
       </c>
       <c r="B27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C27" t="s">
-        <v>548</v>
+        <v>30</v>
       </c>
       <c r="D27">
-        <f t="shared" si="0"/>
-        <v>187</v>
+        <f>VLOOKUP(C27,$G$2:$H$1211,2,FALSE)</f>
+        <v>196</v>
       </c>
       <c r="G27" t="s">
         <v>94</v>
@@ -5589,14 +5645,14 @@
         <v>20</v>
       </c>
       <c r="B28">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C28" t="s">
-        <v>43</v>
+        <v>897</v>
       </c>
       <c r="D28">
-        <f t="shared" si="0"/>
-        <v>17</v>
+        <f>VLOOKUP(C28,$G$2:$H$1211,2,FALSE)</f>
+        <v>312</v>
       </c>
       <c r="G28" t="s">
         <v>95</v>
@@ -5610,14 +5666,14 @@
         <v>20</v>
       </c>
       <c r="B29">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C29" t="s">
-        <v>826</v>
+        <v>602</v>
       </c>
       <c r="D29">
-        <f t="shared" si="0"/>
-        <v>284</v>
+        <f>VLOOKUP(C29,$G$2:$H$1211,2,FALSE)</f>
+        <v>204</v>
       </c>
       <c r="G29" t="s">
         <v>96</v>
@@ -5631,14 +5687,14 @@
         <v>20</v>
       </c>
       <c r="B30">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C30" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D30">
-        <f t="shared" si="0"/>
-        <v>116</v>
+        <f>VLOOKUP(C30,$G$2:$H$1211,2,FALSE)</f>
+        <v>129</v>
       </c>
       <c r="G30" t="s">
         <v>97</v>
@@ -5652,14 +5708,14 @@
         <v>20</v>
       </c>
       <c r="B31">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C31" t="s">
-        <v>589</v>
+        <v>50</v>
       </c>
       <c r="D31">
-        <f t="shared" si="0"/>
-        <v>198</v>
+        <f>VLOOKUP(C31,$G$2:$H$1211,2,FALSE)</f>
+        <v>150</v>
       </c>
       <c r="G31" t="s">
         <v>98</v>
@@ -5673,14 +5729,14 @@
         <v>20</v>
       </c>
       <c r="B32">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C32" t="s">
-        <v>705</v>
+        <v>156</v>
       </c>
       <c r="D32">
-        <f t="shared" si="0"/>
-        <v>243</v>
+        <f>VLOOKUP(C32,$G$2:$H$1211,2,FALSE)</f>
+        <v>36</v>
       </c>
       <c r="G32" t="s">
         <v>99</v>
@@ -5694,14 +5750,14 @@
         <v>20</v>
       </c>
       <c r="B33">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C33" t="s">
-        <v>570</v>
+        <v>934</v>
       </c>
       <c r="D33">
-        <f t="shared" si="0"/>
-        <v>193</v>
+        <f>VLOOKUP(C33,$G$2:$H$1211,2,FALSE)</f>
+        <v>326</v>
       </c>
       <c r="G33" t="s">
         <v>54</v>
@@ -5712,17 +5768,17 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B34">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C34" t="s">
-        <v>1064</v>
+        <v>705</v>
       </c>
       <c r="D34">
-        <f t="shared" si="0"/>
-        <v>62</v>
+        <f>VLOOKUP(C34,$G$2:$H$1211,2,FALSE)</f>
+        <v>243</v>
       </c>
       <c r="G34" t="s">
         <v>100</v>
@@ -5733,17 +5789,17 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B35">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C35" t="s">
-        <v>58</v>
+        <v>372</v>
       </c>
       <c r="D35">
-        <f t="shared" si="0"/>
-        <v>91</v>
+        <f>VLOOKUP(C35,$G$2:$H$1211,2,FALSE)</f>
+        <v>121</v>
       </c>
       <c r="G35" t="s">
         <v>101</v>
@@ -5754,17 +5810,17 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B36">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C36" t="s">
-        <v>56</v>
+        <v>126</v>
       </c>
       <c r="D36">
-        <f t="shared" si="0"/>
-        <v>119</v>
+        <f>VLOOKUP(C36,$G$2:$H$1211,2,FALSE)</f>
+        <v>24</v>
       </c>
       <c r="G36" t="s">
         <v>102</v>
@@ -5778,14 +5834,14 @@
         <v>37</v>
       </c>
       <c r="B37">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C37" t="s">
-        <v>8</v>
+        <v>1064</v>
       </c>
       <c r="D37">
-        <f t="shared" si="0"/>
-        <v>317</v>
+        <f>VLOOKUP(C37,$G$2:$H$1211,2,FALSE)</f>
+        <v>62</v>
       </c>
       <c r="G37" t="s">
         <v>103</v>
@@ -5799,14 +5855,14 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C38" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="D38">
-        <f t="shared" si="0"/>
-        <v>308</v>
+        <f>VLOOKUP(C38,$G$2:$H$1211,2,FALSE)</f>
+        <v>91</v>
       </c>
       <c r="G38" t="s">
         <v>104</v>
@@ -5820,14 +5876,14 @@
         <v>37</v>
       </c>
       <c r="B39">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C39" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D39">
-        <f t="shared" si="0"/>
-        <v>355</v>
+        <f>VLOOKUP(C39,$G$2:$H$1211,2,FALSE)</f>
+        <v>248</v>
       </c>
       <c r="G39" t="s">
         <v>59</v>
@@ -5841,14 +5897,14 @@
         <v>37</v>
       </c>
       <c r="B40">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C40" t="s">
-        <v>764</v>
+        <v>8</v>
       </c>
       <c r="D40">
-        <f t="shared" si="0"/>
-        <v>265</v>
+        <f>VLOOKUP(C40,$G$2:$H$1211,2,FALSE)</f>
+        <v>317</v>
       </c>
       <c r="G40" t="s">
         <v>105</v>
@@ -5862,14 +5918,14 @@
         <v>37</v>
       </c>
       <c r="B41">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C41" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="D41">
-        <f t="shared" si="0"/>
-        <v>196</v>
+        <f>VLOOKUP(C41,$G$2:$H$1211,2,FALSE)</f>
+        <v>13</v>
       </c>
       <c r="G41" t="s">
         <v>106</v>
@@ -5883,14 +5939,14 @@
         <v>37</v>
       </c>
       <c r="B42">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C42" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D42">
-        <f t="shared" si="0"/>
-        <v>331</v>
+        <f>VLOOKUP(C42,$G$2:$H$1211,2,FALSE)</f>
+        <v>19</v>
       </c>
       <c r="G42" t="s">
         <v>107</v>
@@ -5904,14 +5960,14 @@
         <v>37</v>
       </c>
       <c r="B43">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C43" t="s">
-        <v>897</v>
+        <v>29</v>
       </c>
       <c r="D43">
-        <f t="shared" si="0"/>
-        <v>312</v>
+        <f>VLOOKUP(C43,$G$2:$H$1211,2,FALSE)</f>
+        <v>347</v>
       </c>
       <c r="G43" t="s">
         <v>108</v>
@@ -5925,14 +5981,14 @@
         <v>37</v>
       </c>
       <c r="B44">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C44" t="s">
-        <v>799</v>
+        <v>62</v>
       </c>
       <c r="D44">
-        <f t="shared" si="0"/>
-        <v>274</v>
+        <f>VLOOKUP(C44,$G$2:$H$1211,2,FALSE)</f>
+        <v>177</v>
       </c>
       <c r="G44" t="s">
         <v>109</v>
@@ -5946,14 +6002,14 @@
         <v>37</v>
       </c>
       <c r="B45">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C45" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="D45">
-        <f t="shared" si="0"/>
-        <v>150</v>
+        <f>VLOOKUP(C45,$G$2:$H$1211,2,FALSE)</f>
+        <v>104</v>
       </c>
       <c r="G45" t="s">
         <v>110</v>
@@ -5967,14 +6023,14 @@
         <v>37</v>
       </c>
       <c r="B46">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C46" t="s">
-        <v>634</v>
+        <v>45</v>
       </c>
       <c r="D46">
-        <f t="shared" si="0"/>
-        <v>215</v>
+        <f>VLOOKUP(C46,$G$2:$H$1211,2,FALSE)</f>
+        <v>331</v>
       </c>
       <c r="G46" t="s">
         <v>111</v>
@@ -5988,14 +6044,14 @@
         <v>37</v>
       </c>
       <c r="B47">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C47" t="s">
-        <v>269</v>
+        <v>899</v>
       </c>
       <c r="D47">
-        <f t="shared" si="0"/>
-        <v>79</v>
+        <f>VLOOKUP(C47,$G$2:$H$1211,2,FALSE)</f>
+        <v>313</v>
       </c>
       <c r="G47" t="s">
         <v>17</v>
@@ -6009,14 +6065,14 @@
         <v>37</v>
       </c>
       <c r="B48">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C48" t="s">
-        <v>490</v>
+        <v>826</v>
       </c>
       <c r="D48">
-        <f t="shared" si="0"/>
-        <v>167</v>
+        <f>VLOOKUP(C48,$G$2:$H$1211,2,FALSE)</f>
+        <v>284</v>
       </c>
       <c r="G48" t="s">
         <v>112</v>
@@ -6030,14 +6086,14 @@
         <v>37</v>
       </c>
       <c r="B49">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C49" t="s">
-        <v>945</v>
+        <v>868</v>
       </c>
       <c r="D49">
-        <f t="shared" si="0"/>
-        <v>332</v>
+        <f>VLOOKUP(C49,$G$2:$H$1211,2,FALSE)</f>
+        <v>299</v>
       </c>
       <c r="G49" t="s">
         <v>113</v>
@@ -6048,17 +6104,17 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="B50">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C50" t="s">
-        <v>54</v>
+        <v>926</v>
       </c>
       <c r="D50">
-        <f t="shared" si="0"/>
-        <v>11</v>
+        <f>VLOOKUP(C50,$G$2:$H$1211,2,FALSE)</f>
+        <v>321</v>
       </c>
       <c r="G50" t="s">
         <v>114</v>
@@ -6069,17 +6125,17 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="B51">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C51" t="s">
-        <v>7</v>
+        <v>513</v>
       </c>
       <c r="D51">
-        <f t="shared" si="0"/>
-        <v>125</v>
+        <f>VLOOKUP(C51,$G$2:$H$1211,2,FALSE)</f>
+        <v>176</v>
       </c>
       <c r="G51" t="s">
         <v>43</v>
@@ -6090,17 +6146,17 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="B52">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C52" t="s">
-        <v>22</v>
+        <v>432</v>
       </c>
       <c r="D52">
-        <f t="shared" si="0"/>
-        <v>108</v>
+        <f>VLOOKUP(C52,$G$2:$H$1211,2,FALSE)</f>
+        <v>143</v>
       </c>
       <c r="G52" t="s">
         <v>115</v>
@@ -6111,17 +6167,17 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="B53">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C53" t="s">
-        <v>522</v>
+        <v>945</v>
       </c>
       <c r="D53">
-        <f t="shared" si="0"/>
-        <v>180</v>
+        <f>VLOOKUP(C53,$G$2:$H$1211,2,FALSE)</f>
+        <v>332</v>
       </c>
       <c r="G53" t="s">
         <v>116</v>
@@ -6135,14 +6191,14 @@
         <v>53</v>
       </c>
       <c r="B54">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C54" t="s">
-        <v>6</v>
+        <v>54</v>
       </c>
       <c r="D54">
-        <f t="shared" si="0"/>
-        <v>353</v>
+        <f>VLOOKUP(C54,$G$2:$H$1211,2,FALSE)</f>
+        <v>11</v>
       </c>
       <c r="G54" t="s">
         <v>39</v>
@@ -6156,14 +6212,14 @@
         <v>53</v>
       </c>
       <c r="B55">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C55" t="s">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="D55">
-        <f t="shared" si="0"/>
-        <v>19</v>
+        <f>VLOOKUP(C55,$G$2:$H$1211,2,FALSE)</f>
+        <v>125</v>
       </c>
       <c r="G55" t="s">
         <v>117</v>
@@ -6177,14 +6233,14 @@
         <v>53</v>
       </c>
       <c r="B56">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C56" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="D56">
-        <f t="shared" si="0"/>
-        <v>142</v>
+        <f>VLOOKUP(C56,$G$2:$H$1211,2,FALSE)</f>
+        <v>138</v>
       </c>
       <c r="G56" t="s">
         <v>118</v>
@@ -6198,14 +6254,14 @@
         <v>53</v>
       </c>
       <c r="B57">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C57" t="s">
-        <v>768</v>
+        <v>23</v>
       </c>
       <c r="D57">
-        <f t="shared" si="0"/>
-        <v>266</v>
+        <f>VLOOKUP(C57,$G$2:$H$1211,2,FALSE)</f>
+        <v>4</v>
       </c>
       <c r="G57" t="s">
         <v>119</v>
@@ -6219,14 +6275,14 @@
         <v>53</v>
       </c>
       <c r="B58">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C58" t="s">
-        <v>28</v>
+        <v>857</v>
       </c>
       <c r="D58">
-        <f t="shared" si="0"/>
-        <v>55</v>
+        <f>VLOOKUP(C58,$G$2:$H$1211,2,FALSE)</f>
+        <v>296</v>
       </c>
       <c r="G58" t="s">
         <v>120</v>
@@ -6240,14 +6296,14 @@
         <v>53</v>
       </c>
       <c r="B59">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C59" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="D59">
-        <f t="shared" si="0"/>
-        <v>260</v>
+        <f>VLOOKUP(C59,$G$2:$H$1211,2,FALSE)</f>
+        <v>142</v>
       </c>
       <c r="G59" t="s">
         <v>121</v>
@@ -6261,14 +6317,14 @@
         <v>53</v>
       </c>
       <c r="B60">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C60" t="s">
-        <v>787</v>
+        <v>768</v>
       </c>
       <c r="D60">
-        <f t="shared" si="0"/>
-        <v>271</v>
+        <f>VLOOKUP(C60,$G$2:$H$1211,2,FALSE)</f>
+        <v>266</v>
       </c>
       <c r="G60" t="s">
         <v>122</v>
@@ -6282,14 +6338,14 @@
         <v>53</v>
       </c>
       <c r="B61">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C61" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="D61">
-        <f t="shared" si="0"/>
-        <v>23</v>
+        <f>VLOOKUP(C61,$G$2:$H$1211,2,FALSE)</f>
+        <v>55</v>
       </c>
       <c r="G61" t="s">
         <v>13</v>
@@ -6303,14 +6359,14 @@
         <v>53</v>
       </c>
       <c r="B62">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C62" t="s">
-        <v>868</v>
+        <v>548</v>
       </c>
       <c r="D62">
-        <f t="shared" si="0"/>
-        <v>299</v>
+        <f>VLOOKUP(C62,$G$2:$H$1211,2,FALSE)</f>
+        <v>187</v>
       </c>
       <c r="G62" t="s">
         <v>1065</v>
@@ -6324,14 +6380,14 @@
         <v>53</v>
       </c>
       <c r="B63">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C63" t="s">
-        <v>934</v>
+        <v>60</v>
       </c>
       <c r="D63">
-        <f t="shared" si="0"/>
-        <v>326</v>
+        <f>VLOOKUP(C63,$G$2:$H$1211,2,FALSE)</f>
+        <v>260</v>
       </c>
       <c r="G63" t="s">
         <v>123</v>
@@ -6345,14 +6401,14 @@
         <v>53</v>
       </c>
       <c r="B64">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C64" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="D64">
-        <f t="shared" si="0"/>
-        <v>176</v>
+        <f>VLOOKUP(C64,$G$2:$H$1211,2,FALSE)</f>
+        <v>178</v>
       </c>
       <c r="G64" t="s">
         <v>124</v>
@@ -6366,14 +6422,14 @@
         <v>53</v>
       </c>
       <c r="B65">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C65" t="s">
-        <v>990</v>
+        <v>15</v>
       </c>
       <c r="D65">
-        <f t="shared" si="0"/>
-        <v>348</v>
+        <f>VLOOKUP(C65,$G$2:$H$1211,2,FALSE)</f>
+        <v>23</v>
       </c>
       <c r="G65" t="s">
         <v>125</v>
@@ -6383,6 +6439,19 @@
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>53</v>
+      </c>
+      <c r="B66">
+        <v>13</v>
+      </c>
+      <c r="C66" t="s">
+        <v>66</v>
+      </c>
+      <c r="D66">
+        <f>VLOOKUP(C66,$G$2:$H$1211,2,FALSE)</f>
+        <v>116</v>
+      </c>
       <c r="G66" t="s">
         <v>15</v>
       </c>
@@ -6391,6 +6460,19 @@
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>53</v>
+      </c>
+      <c r="B67">
+        <v>14</v>
+      </c>
+      <c r="C67" t="s">
+        <v>589</v>
+      </c>
+      <c r="D67">
+        <f>VLOOKUP(C67,$G$2:$H$1211,2,FALSE)</f>
+        <v>198</v>
+      </c>
       <c r="G67" t="s">
         <v>126</v>
       </c>
@@ -6399,6 +6481,19 @@
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>53</v>
+      </c>
+      <c r="B68">
+        <v>15</v>
+      </c>
+      <c r="C68" t="s">
+        <v>269</v>
+      </c>
+      <c r="D68">
+        <f>VLOOKUP(C68,$G$2:$H$1211,2,FALSE)</f>
+        <v>79</v>
+      </c>
       <c r="G68" t="s">
         <v>127</v>
       </c>
@@ -6407,6 +6502,19 @@
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>53</v>
+      </c>
+      <c r="B69">
+        <v>16</v>
+      </c>
+      <c r="C69" t="s">
+        <v>893</v>
+      </c>
+      <c r="D69">
+        <f>VLOOKUP(C69,$G$2:$H$1211,2,FALSE)</f>
+        <v>310</v>
+      </c>
       <c r="G69" t="s">
         <v>128</v>
       </c>

--- a/L1/data/bracketology/espn_bracketology_2026.xlsx
+++ b/L1/data/bracketology/espn_bracketology_2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ryanbrowder/Documents/Projects/marchMadness/L1/data/bracketology/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04327F0B-DC9B-2545-87C8-CE1011EFB3F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B76C8901-0F27-3B48-9875-8595A84AF9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11820" yWindow="780" windowWidth="17060" windowHeight="17180" xr2:uid="{F87E21A2-B3CC-9145-B55E-990F91045160}"/>
   </bookViews>
@@ -4134,7 +4134,7 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D3">
         <v>180</v>
@@ -4148,7 +4148,7 @@
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>401</v>
       </c>
       <c r="D4">
         <v>133</v>
@@ -4162,10 +4162,10 @@
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D5">
-        <v>108</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -4176,10 +4176,10 @@
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>857</v>
       </c>
       <c r="D6">
-        <v>308</v>
+        <v>296</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -4190,10 +4190,10 @@
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D7">
-        <v>159</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -4204,10 +4204,10 @@
         <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D8">
-        <v>355</v>
+        <v>177</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -4218,10 +4218,10 @@
         <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>764</v>
+        <v>29</v>
       </c>
       <c r="D9">
-        <v>265</v>
+        <v>347</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -4232,10 +4232,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="D10">
-        <v>132</v>
+        <v>331</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
@@ -4246,10 +4246,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>878</v>
+        <v>548</v>
       </c>
       <c r="D11">
-        <v>304</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
@@ -4260,10 +4260,10 @@
         <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>799</v>
+        <v>60</v>
       </c>
       <c r="D12">
-        <v>274</v>
+        <v>260</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
@@ -4274,10 +4274,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="D13">
-        <v>229</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
@@ -4288,10 +4288,10 @@
         <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="D14">
-        <v>380</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
@@ -4316,10 +4316,10 @@
         <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>634</v>
+        <v>926</v>
       </c>
       <c r="D16">
-        <v>215</v>
+        <v>321</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
@@ -4400,10 +4400,10 @@
         <v>4</v>
       </c>
       <c r="C22" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D22">
-        <v>356</v>
+        <v>138</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
@@ -4414,10 +4414,10 @@
         <v>5</v>
       </c>
       <c r="C23" t="s">
-        <v>6</v>
+        <v>59</v>
       </c>
       <c r="D23">
-        <v>353</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
@@ -4428,10 +4428,10 @@
         <v>6</v>
       </c>
       <c r="C24" t="s">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="D24">
-        <v>211</v>
+        <v>353</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
@@ -4442,10 +4442,10 @@
         <v>7</v>
       </c>
       <c r="C25" t="s">
-        <v>12</v>
+        <v>768</v>
       </c>
       <c r="D25">
-        <v>374</v>
+        <v>266</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
@@ -4456,10 +4456,10 @@
         <v>8</v>
       </c>
       <c r="C26" t="s">
-        <v>944</v>
+        <v>28</v>
       </c>
       <c r="D26">
-        <v>330</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
@@ -4470,10 +4470,10 @@
         <v>9</v>
       </c>
       <c r="C27" t="s">
-        <v>30</v>
+        <v>944</v>
       </c>
       <c r="D27">
-        <v>196</v>
+        <v>330</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
@@ -4484,10 +4484,10 @@
         <v>10</v>
       </c>
       <c r="C28" t="s">
-        <v>897</v>
+        <v>47</v>
       </c>
       <c r="D28">
-        <v>312</v>
+        <v>229</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
@@ -4498,10 +4498,10 @@
         <v>11</v>
       </c>
       <c r="C29" t="s">
-        <v>602</v>
+        <v>519</v>
       </c>
       <c r="D29">
-        <v>204</v>
+        <v>178</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
@@ -4509,13 +4509,13 @@
         <v>20</v>
       </c>
       <c r="B30">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C30" t="s">
-        <v>61</v>
+        <v>826</v>
       </c>
       <c r="D30">
-        <v>129</v>
+        <v>284</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
@@ -4523,13 +4523,13 @@
         <v>20</v>
       </c>
       <c r="B31">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C31" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="D31">
-        <v>150</v>
+        <v>116</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
@@ -4537,13 +4537,13 @@
         <v>20</v>
       </c>
       <c r="B32">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C32" t="s">
-        <v>156</v>
+        <v>589</v>
       </c>
       <c r="D32">
-        <v>36</v>
+        <v>198</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
@@ -4551,13 +4551,13 @@
         <v>20</v>
       </c>
       <c r="B33">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C33" t="s">
-        <v>934</v>
+        <v>269</v>
       </c>
       <c r="D33">
-        <v>326</v>
+        <v>79</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
@@ -4565,13 +4565,13 @@
         <v>20</v>
       </c>
       <c r="B34">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C34" t="s">
-        <v>705</v>
+        <v>372</v>
       </c>
       <c r="D34">
-        <v>243</v>
+        <v>121</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
@@ -4582,24 +4582,24 @@
         <v>16</v>
       </c>
       <c r="C35" t="s">
-        <v>372</v>
+        <v>127</v>
       </c>
       <c r="D35">
-        <v>121</v>
+        <v>24</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="B36">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C36" t="s">
-        <v>126</v>
+        <v>1064</v>
       </c>
       <c r="D36">
-        <v>24</v>
+        <v>62</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
@@ -4607,13 +4607,13 @@
         <v>37</v>
       </c>
       <c r="B37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C37" t="s">
-        <v>1064</v>
+        <v>58</v>
       </c>
       <c r="D37">
-        <v>62</v>
+        <v>91</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
@@ -4621,13 +4621,13 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C38" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D38">
-        <v>91</v>
+        <v>248</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
@@ -4635,13 +4635,13 @@
         <v>37</v>
       </c>
       <c r="B39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C39" t="s">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="D39">
-        <v>248</v>
+        <v>356</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
@@ -4649,13 +4649,13 @@
         <v>37</v>
       </c>
       <c r="B40">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C40" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D40">
-        <v>317</v>
+        <v>308</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
@@ -4663,13 +4663,13 @@
         <v>37</v>
       </c>
       <c r="B41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C41" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="D41">
-        <v>13</v>
+        <v>159</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
@@ -4677,13 +4677,13 @@
         <v>37</v>
       </c>
       <c r="B42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C42" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="D42">
-        <v>19</v>
+        <v>355</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
@@ -4691,13 +4691,13 @@
         <v>37</v>
       </c>
       <c r="B43">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C43" t="s">
-        <v>29</v>
+        <v>764</v>
       </c>
       <c r="D43">
-        <v>347</v>
+        <v>265</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
@@ -4705,13 +4705,13 @@
         <v>37</v>
       </c>
       <c r="B44">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C44" t="s">
-        <v>62</v>
+        <v>10</v>
       </c>
       <c r="D44">
-        <v>177</v>
+        <v>132</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
@@ -4719,13 +4719,13 @@
         <v>37</v>
       </c>
       <c r="B45">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C45" t="s">
-        <v>11</v>
+        <v>899</v>
       </c>
       <c r="D45">
-        <v>104</v>
+        <v>313</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
@@ -4733,13 +4733,13 @@
         <v>37</v>
       </c>
       <c r="B46">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C46" t="s">
-        <v>45</v>
+        <v>799</v>
       </c>
       <c r="D46">
-        <v>331</v>
+        <v>274</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
@@ -4750,10 +4750,10 @@
         <v>11</v>
       </c>
       <c r="C47" t="s">
-        <v>899</v>
+        <v>602</v>
       </c>
       <c r="D47">
-        <v>313</v>
+        <v>204</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
@@ -4764,10 +4764,10 @@
         <v>12</v>
       </c>
       <c r="C48" t="s">
-        <v>826</v>
+        <v>50</v>
       </c>
       <c r="D48">
-        <v>284</v>
+        <v>150</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
@@ -4778,10 +4778,10 @@
         <v>13</v>
       </c>
       <c r="C49" t="s">
-        <v>868</v>
+        <v>156</v>
       </c>
       <c r="D49">
-        <v>299</v>
+        <v>36</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
@@ -4792,10 +4792,10 @@
         <v>14</v>
       </c>
       <c r="C50" t="s">
-        <v>926</v>
+        <v>634</v>
       </c>
       <c r="D50">
-        <v>321</v>
+        <v>215</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
@@ -4820,10 +4820,10 @@
         <v>16</v>
       </c>
       <c r="C52" t="s">
-        <v>432</v>
+        <v>893</v>
       </c>
       <c r="D52">
-        <v>143</v>
+        <v>310</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
@@ -4834,10 +4834,10 @@
         <v>16</v>
       </c>
       <c r="C53" t="s">
-        <v>945</v>
+        <v>432</v>
       </c>
       <c r="D53">
-        <v>332</v>
+        <v>143</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
@@ -4876,10 +4876,10 @@
         <v>3</v>
       </c>
       <c r="C56" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D56">
-        <v>138</v>
+        <v>108</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
@@ -4890,10 +4890,10 @@
         <v>4</v>
       </c>
       <c r="C57" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D57">
-        <v>4</v>
+        <v>317</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
@@ -4904,10 +4904,10 @@
         <v>5</v>
       </c>
       <c r="C58" t="s">
-        <v>857</v>
+        <v>57</v>
       </c>
       <c r="D58">
-        <v>296</v>
+        <v>211</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
@@ -4918,10 +4918,10 @@
         <v>6</v>
       </c>
       <c r="C59" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="D59">
-        <v>142</v>
+        <v>374</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
@@ -4932,10 +4932,10 @@
         <v>7</v>
       </c>
       <c r="C60" t="s">
-        <v>768</v>
+        <v>39</v>
       </c>
       <c r="D60">
-        <v>266</v>
+        <v>19</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
@@ -4946,10 +4946,10 @@
         <v>8</v>
       </c>
       <c r="C61" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D61">
-        <v>55</v>
+        <v>104</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
@@ -4960,10 +4960,10 @@
         <v>9</v>
       </c>
       <c r="C62" t="s">
-        <v>548</v>
+        <v>30</v>
       </c>
       <c r="D62">
-        <v>187</v>
+        <v>196</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
@@ -4974,10 +4974,10 @@
         <v>10</v>
       </c>
       <c r="C63" t="s">
-        <v>60</v>
+        <v>878</v>
       </c>
       <c r="D63">
-        <v>260</v>
+        <v>304</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
@@ -4988,10 +4988,10 @@
         <v>11</v>
       </c>
       <c r="C64" t="s">
-        <v>519</v>
+        <v>897</v>
       </c>
       <c r="D64">
-        <v>178</v>
+        <v>312</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
@@ -5002,10 +5002,10 @@
         <v>12</v>
       </c>
       <c r="C65" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="D65">
-        <v>23</v>
+        <v>380</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
@@ -5016,10 +5016,10 @@
         <v>13</v>
       </c>
       <c r="C66" t="s">
-        <v>66</v>
+        <v>868</v>
       </c>
       <c r="D66">
-        <v>116</v>
+        <v>299</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
@@ -5030,10 +5030,10 @@
         <v>14</v>
       </c>
       <c r="C67" t="s">
-        <v>589</v>
+        <v>934</v>
       </c>
       <c r="D67">
-        <v>198</v>
+        <v>326</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
@@ -5044,10 +5044,10 @@
         <v>15</v>
       </c>
       <c r="C68" t="s">
-        <v>269</v>
+        <v>705</v>
       </c>
       <c r="D68">
-        <v>79</v>
+        <v>243</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
@@ -5058,10 +5058,10 @@
         <v>16</v>
       </c>
       <c r="C69" t="s">
-        <v>893</v>
+        <v>945</v>
       </c>
       <c r="D69">
-        <v>310</v>
+        <v>332</v>
       </c>
     </row>
   </sheetData>
@@ -5123,10 +5123,10 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D3">
-        <f t="shared" ref="D3:D65" si="0">VLOOKUP(C3,$G$2:$H$1211,2,FALSE)</f>
+        <f t="shared" ref="D3:D13" si="0">VLOOKUP(C3,$G$2:$H$1211,2,FALSE)</f>
         <v>180</v>
       </c>
       <c r="G3" t="s">
@@ -5144,7 +5144,7 @@
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>401</v>
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
@@ -5165,11 +5165,11 @@
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
-        <v>108</v>
+        <v>4</v>
       </c>
       <c r="G5" t="s">
         <v>74</v>
@@ -5186,11 +5186,11 @@
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>857</v>
       </c>
       <c r="D6">
         <f t="shared" si="0"/>
-        <v>308</v>
+        <v>296</v>
       </c>
       <c r="G6" t="s">
         <v>75</v>
@@ -5207,11 +5207,11 @@
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="G7" t="s">
         <v>76</v>
@@ -5228,11 +5228,11 @@
         <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
-        <v>355</v>
+        <v>177</v>
       </c>
       <c r="G8" t="s">
         <v>64</v>
@@ -5249,11 +5249,11 @@
         <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>764</v>
+        <v>29</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
-        <v>265</v>
+        <v>347</v>
       </c>
       <c r="G9" t="s">
         <v>77</v>
@@ -5270,11 +5270,11 @@
         <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
-        <v>132</v>
+        <v>331</v>
       </c>
       <c r="G10" t="s">
         <v>23</v>
@@ -5291,11 +5291,11 @@
         <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>878</v>
+        <v>548</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
-        <v>304</v>
+        <v>187</v>
       </c>
       <c r="G11" t="s">
         <v>78</v>
@@ -5312,11 +5312,11 @@
         <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>799</v>
+        <v>60</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
-        <v>274</v>
+        <v>260</v>
       </c>
       <c r="G12" t="s">
         <v>79</v>
@@ -5333,11 +5333,11 @@
         <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="D13">
         <f t="shared" si="0"/>
-        <v>229</v>
+        <v>129</v>
       </c>
       <c r="G13" t="s">
         <v>80</v>
@@ -5354,11 +5354,11 @@
         <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="D14">
-        <f>VLOOKUP(C14,$G$2:$H$1211,2,FALSE)</f>
-        <v>380</v>
+        <f t="shared" ref="D14:D45" si="1">VLOOKUP(C14,$G$2:$H$1211,2,FALSE)</f>
+        <v>23</v>
       </c>
       <c r="G14" t="s">
         <v>81</v>
@@ -5378,7 +5378,7 @@
         <v>16</v>
       </c>
       <c r="D15">
-        <f>VLOOKUP(C15,$G$2:$H$1211,2,FALSE)</f>
+        <f t="shared" si="1"/>
         <v>337</v>
       </c>
       <c r="G15" t="s">
@@ -5396,11 +5396,11 @@
         <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>634</v>
+        <v>926</v>
       </c>
       <c r="D16">
-        <f>VLOOKUP(C16,$G$2:$H$1211,2,FALSE)</f>
-        <v>215</v>
+        <f t="shared" si="1"/>
+        <v>321</v>
       </c>
       <c r="G16" t="s">
         <v>83</v>
@@ -5420,7 +5420,7 @@
         <v>1052</v>
       </c>
       <c r="D17">
-        <f>VLOOKUP(C17,$G$2:$H$1211,2,FALSE)</f>
+        <f t="shared" si="1"/>
         <v>377</v>
       </c>
       <c r="G17" t="s">
@@ -5441,7 +5441,7 @@
         <v>186</v>
       </c>
       <c r="D18">
-        <f>VLOOKUP(C18,$G$2:$H$1211,2,FALSE)</f>
+        <f t="shared" si="1"/>
         <v>45</v>
       </c>
       <c r="G18" t="s">
@@ -5462,7 +5462,7 @@
         <v>21</v>
       </c>
       <c r="D19">
-        <f>VLOOKUP(C19,$G$2:$H$1211,2,FALSE)</f>
+        <f t="shared" si="1"/>
         <v>179</v>
       </c>
       <c r="G19" t="s">
@@ -5483,7 +5483,7 @@
         <v>56</v>
       </c>
       <c r="D20">
-        <f>VLOOKUP(C20,$G$2:$H$1211,2,FALSE)</f>
+        <f t="shared" si="1"/>
         <v>119</v>
       </c>
       <c r="G20" t="s">
@@ -5504,7 +5504,7 @@
         <v>27</v>
       </c>
       <c r="D21">
-        <f>VLOOKUP(C21,$G$2:$H$1211,2,FALSE)</f>
+        <f t="shared" si="1"/>
         <v>199</v>
       </c>
       <c r="G21" t="s">
@@ -5522,11 +5522,11 @@
         <v>4</v>
       </c>
       <c r="C22" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D22">
-        <f>VLOOKUP(C22,$G$2:$H$1211,2,FALSE)</f>
-        <v>356</v>
+        <f t="shared" si="1"/>
+        <v>138</v>
       </c>
       <c r="G22" t="s">
         <v>89</v>
@@ -5543,11 +5543,11 @@
         <v>5</v>
       </c>
       <c r="C23" t="s">
-        <v>6</v>
+        <v>59</v>
       </c>
       <c r="D23">
-        <f>VLOOKUP(C23,$G$2:$H$1211,2,FALSE)</f>
-        <v>353</v>
+        <f t="shared" si="1"/>
+        <v>13</v>
       </c>
       <c r="G23" t="s">
         <v>90</v>
@@ -5564,11 +5564,11 @@
         <v>6</v>
       </c>
       <c r="C24" t="s">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="D24">
-        <f>VLOOKUP(C24,$G$2:$H$1211,2,FALSE)</f>
-        <v>211</v>
+        <f t="shared" si="1"/>
+        <v>353</v>
       </c>
       <c r="G24" t="s">
         <v>91</v>
@@ -5585,11 +5585,11 @@
         <v>7</v>
       </c>
       <c r="C25" t="s">
-        <v>12</v>
+        <v>768</v>
       </c>
       <c r="D25">
-        <f>VLOOKUP(C25,$G$2:$H$1211,2,FALSE)</f>
-        <v>374</v>
+        <f t="shared" si="1"/>
+        <v>266</v>
       </c>
       <c r="G25" t="s">
         <v>92</v>
@@ -5606,11 +5606,11 @@
         <v>8</v>
       </c>
       <c r="C26" t="s">
-        <v>944</v>
+        <v>28</v>
       </c>
       <c r="D26">
-        <f>VLOOKUP(C26,$G$2:$H$1211,2,FALSE)</f>
-        <v>330</v>
+        <f t="shared" si="1"/>
+        <v>55</v>
       </c>
       <c r="G26" t="s">
         <v>93</v>
@@ -5627,11 +5627,11 @@
         <v>9</v>
       </c>
       <c r="C27" t="s">
-        <v>30</v>
+        <v>944</v>
       </c>
       <c r="D27">
-        <f>VLOOKUP(C27,$G$2:$H$1211,2,FALSE)</f>
-        <v>196</v>
+        <f t="shared" si="1"/>
+        <v>330</v>
       </c>
       <c r="G27" t="s">
         <v>94</v>
@@ -5648,11 +5648,11 @@
         <v>10</v>
       </c>
       <c r="C28" t="s">
-        <v>897</v>
+        <v>47</v>
       </c>
       <c r="D28">
-        <f>VLOOKUP(C28,$G$2:$H$1211,2,FALSE)</f>
-        <v>312</v>
+        <f t="shared" si="1"/>
+        <v>229</v>
       </c>
       <c r="G28" t="s">
         <v>95</v>
@@ -5669,11 +5669,11 @@
         <v>11</v>
       </c>
       <c r="C29" t="s">
-        <v>602</v>
+        <v>519</v>
       </c>
       <c r="D29">
-        <f>VLOOKUP(C29,$G$2:$H$1211,2,FALSE)</f>
-        <v>204</v>
+        <f t="shared" si="1"/>
+        <v>178</v>
       </c>
       <c r="G29" t="s">
         <v>96</v>
@@ -5687,14 +5687,14 @@
         <v>20</v>
       </c>
       <c r="B30">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C30" t="s">
-        <v>61</v>
+        <v>826</v>
       </c>
       <c r="D30">
         <f>VLOOKUP(C30,$G$2:$H$1211,2,FALSE)</f>
-        <v>129</v>
+        <v>284</v>
       </c>
       <c r="G30" t="s">
         <v>97</v>
@@ -5708,14 +5708,14 @@
         <v>20</v>
       </c>
       <c r="B31">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C31" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="D31">
         <f>VLOOKUP(C31,$G$2:$H$1211,2,FALSE)</f>
-        <v>150</v>
+        <v>116</v>
       </c>
       <c r="G31" t="s">
         <v>98</v>
@@ -5729,14 +5729,14 @@
         <v>20</v>
       </c>
       <c r="B32">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C32" t="s">
-        <v>156</v>
+        <v>589</v>
       </c>
       <c r="D32">
         <f>VLOOKUP(C32,$G$2:$H$1211,2,FALSE)</f>
-        <v>36</v>
+        <v>198</v>
       </c>
       <c r="G32" t="s">
         <v>99</v>
@@ -5750,14 +5750,14 @@
         <v>20</v>
       </c>
       <c r="B33">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C33" t="s">
-        <v>934</v>
+        <v>269</v>
       </c>
       <c r="D33">
         <f>VLOOKUP(C33,$G$2:$H$1211,2,FALSE)</f>
-        <v>326</v>
+        <v>79</v>
       </c>
       <c r="G33" t="s">
         <v>54</v>
@@ -5771,14 +5771,14 @@
         <v>20</v>
       </c>
       <c r="B34">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C34" t="s">
-        <v>705</v>
+        <v>372</v>
       </c>
       <c r="D34">
         <f>VLOOKUP(C34,$G$2:$H$1211,2,FALSE)</f>
-        <v>243</v>
+        <v>121</v>
       </c>
       <c r="G34" t="s">
         <v>100</v>
@@ -5795,11 +5795,11 @@
         <v>16</v>
       </c>
       <c r="C35" t="s">
-        <v>372</v>
+        <v>127</v>
       </c>
       <c r="D35">
         <f>VLOOKUP(C35,$G$2:$H$1211,2,FALSE)</f>
-        <v>121</v>
+        <v>24</v>
       </c>
       <c r="G35" t="s">
         <v>101</v>
@@ -5810,17 +5810,17 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="B36">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C36" t="s">
-        <v>126</v>
+        <v>1064</v>
       </c>
       <c r="D36">
         <f>VLOOKUP(C36,$G$2:$H$1211,2,FALSE)</f>
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="G36" t="s">
         <v>102</v>
@@ -5834,14 +5834,14 @@
         <v>37</v>
       </c>
       <c r="B37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C37" t="s">
-        <v>1064</v>
+        <v>58</v>
       </c>
       <c r="D37">
         <f>VLOOKUP(C37,$G$2:$H$1211,2,FALSE)</f>
-        <v>62</v>
+        <v>91</v>
       </c>
       <c r="G37" t="s">
         <v>103</v>
@@ -5855,14 +5855,14 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C38" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D38">
         <f>VLOOKUP(C38,$G$2:$H$1211,2,FALSE)</f>
-        <v>91</v>
+        <v>248</v>
       </c>
       <c r="G38" t="s">
         <v>104</v>
@@ -5876,14 +5876,14 @@
         <v>37</v>
       </c>
       <c r="B39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C39" t="s">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="D39">
         <f>VLOOKUP(C39,$G$2:$H$1211,2,FALSE)</f>
-        <v>248</v>
+        <v>356</v>
       </c>
       <c r="G39" t="s">
         <v>59</v>
@@ -5897,14 +5897,14 @@
         <v>37</v>
       </c>
       <c r="B40">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C40" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D40">
         <f>VLOOKUP(C40,$G$2:$H$1211,2,FALSE)</f>
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="G40" t="s">
         <v>105</v>
@@ -5918,14 +5918,14 @@
         <v>37</v>
       </c>
       <c r="B41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C41" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="D41">
         <f>VLOOKUP(C41,$G$2:$H$1211,2,FALSE)</f>
-        <v>13</v>
+        <v>159</v>
       </c>
       <c r="G41" t="s">
         <v>106</v>
@@ -5939,14 +5939,14 @@
         <v>37</v>
       </c>
       <c r="B42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C42" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="D42">
         <f>VLOOKUP(C42,$G$2:$H$1211,2,FALSE)</f>
-        <v>19</v>
+        <v>355</v>
       </c>
       <c r="G42" t="s">
         <v>107</v>
@@ -5960,14 +5960,14 @@
         <v>37</v>
       </c>
       <c r="B43">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C43" t="s">
-        <v>29</v>
+        <v>764</v>
       </c>
       <c r="D43">
         <f>VLOOKUP(C43,$G$2:$H$1211,2,FALSE)</f>
-        <v>347</v>
+        <v>265</v>
       </c>
       <c r="G43" t="s">
         <v>108</v>
@@ -5981,14 +5981,14 @@
         <v>37</v>
       </c>
       <c r="B44">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C44" t="s">
-        <v>62</v>
+        <v>10</v>
       </c>
       <c r="D44">
         <f>VLOOKUP(C44,$G$2:$H$1211,2,FALSE)</f>
-        <v>177</v>
+        <v>132</v>
       </c>
       <c r="G44" t="s">
         <v>109</v>
@@ -6002,14 +6002,14 @@
         <v>37</v>
       </c>
       <c r="B45">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C45" t="s">
-        <v>11</v>
+        <v>899</v>
       </c>
       <c r="D45">
         <f>VLOOKUP(C45,$G$2:$H$1211,2,FALSE)</f>
-        <v>104</v>
+        <v>313</v>
       </c>
       <c r="G45" t="s">
         <v>110</v>
@@ -6023,14 +6023,14 @@
         <v>37</v>
       </c>
       <c r="B46">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C46" t="s">
-        <v>45</v>
+        <v>799</v>
       </c>
       <c r="D46">
         <f>VLOOKUP(C46,$G$2:$H$1211,2,FALSE)</f>
-        <v>331</v>
+        <v>274</v>
       </c>
       <c r="G46" t="s">
         <v>111</v>
@@ -6047,11 +6047,11 @@
         <v>11</v>
       </c>
       <c r="C47" t="s">
-        <v>899</v>
+        <v>602</v>
       </c>
       <c r="D47">
         <f>VLOOKUP(C47,$G$2:$H$1211,2,FALSE)</f>
-        <v>313</v>
+        <v>204</v>
       </c>
       <c r="G47" t="s">
         <v>17</v>
@@ -6068,11 +6068,11 @@
         <v>12</v>
       </c>
       <c r="C48" t="s">
-        <v>826</v>
+        <v>50</v>
       </c>
       <c r="D48">
         <f>VLOOKUP(C48,$G$2:$H$1211,2,FALSE)</f>
-        <v>284</v>
+        <v>150</v>
       </c>
       <c r="G48" t="s">
         <v>112</v>
@@ -6089,11 +6089,11 @@
         <v>13</v>
       </c>
       <c r="C49" t="s">
-        <v>868</v>
+        <v>156</v>
       </c>
       <c r="D49">
         <f>VLOOKUP(C49,$G$2:$H$1211,2,FALSE)</f>
-        <v>299</v>
+        <v>36</v>
       </c>
       <c r="G49" t="s">
         <v>113</v>
@@ -6110,11 +6110,11 @@
         <v>14</v>
       </c>
       <c r="C50" t="s">
-        <v>926</v>
+        <v>634</v>
       </c>
       <c r="D50">
         <f>VLOOKUP(C50,$G$2:$H$1211,2,FALSE)</f>
-        <v>321</v>
+        <v>215</v>
       </c>
       <c r="G50" t="s">
         <v>114</v>
@@ -6152,11 +6152,11 @@
         <v>16</v>
       </c>
       <c r="C52" t="s">
-        <v>432</v>
+        <v>893</v>
       </c>
       <c r="D52">
         <f>VLOOKUP(C52,$G$2:$H$1211,2,FALSE)</f>
-        <v>143</v>
+        <v>310</v>
       </c>
       <c r="G52" t="s">
         <v>115</v>
@@ -6173,11 +6173,11 @@
         <v>16</v>
       </c>
       <c r="C53" t="s">
-        <v>945</v>
+        <v>432</v>
       </c>
       <c r="D53">
         <f>VLOOKUP(C53,$G$2:$H$1211,2,FALSE)</f>
-        <v>332</v>
+        <v>143</v>
       </c>
       <c r="G53" t="s">
         <v>116</v>
@@ -6236,11 +6236,11 @@
         <v>3</v>
       </c>
       <c r="C56" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D56">
         <f>VLOOKUP(C56,$G$2:$H$1211,2,FALSE)</f>
-        <v>138</v>
+        <v>108</v>
       </c>
       <c r="G56" t="s">
         <v>118</v>
@@ -6257,11 +6257,11 @@
         <v>4</v>
       </c>
       <c r="C57" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D57">
         <f>VLOOKUP(C57,$G$2:$H$1211,2,FALSE)</f>
-        <v>4</v>
+        <v>317</v>
       </c>
       <c r="G57" t="s">
         <v>119</v>
@@ -6278,11 +6278,11 @@
         <v>5</v>
       </c>
       <c r="C58" t="s">
-        <v>857</v>
+        <v>57</v>
       </c>
       <c r="D58">
         <f>VLOOKUP(C58,$G$2:$H$1211,2,FALSE)</f>
-        <v>296</v>
+        <v>211</v>
       </c>
       <c r="G58" t="s">
         <v>120</v>
@@ -6299,11 +6299,11 @@
         <v>6</v>
       </c>
       <c r="C59" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="D59">
         <f>VLOOKUP(C59,$G$2:$H$1211,2,FALSE)</f>
-        <v>142</v>
+        <v>374</v>
       </c>
       <c r="G59" t="s">
         <v>121</v>
@@ -6320,11 +6320,11 @@
         <v>7</v>
       </c>
       <c r="C60" t="s">
-        <v>768</v>
+        <v>39</v>
       </c>
       <c r="D60">
         <f>VLOOKUP(C60,$G$2:$H$1211,2,FALSE)</f>
-        <v>266</v>
+        <v>19</v>
       </c>
       <c r="G60" t="s">
         <v>122</v>
@@ -6341,11 +6341,11 @@
         <v>8</v>
       </c>
       <c r="C61" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D61">
         <f>VLOOKUP(C61,$G$2:$H$1211,2,FALSE)</f>
-        <v>55</v>
+        <v>104</v>
       </c>
       <c r="G61" t="s">
         <v>13</v>
@@ -6362,11 +6362,11 @@
         <v>9</v>
       </c>
       <c r="C62" t="s">
-        <v>548</v>
+        <v>30</v>
       </c>
       <c r="D62">
         <f>VLOOKUP(C62,$G$2:$H$1211,2,FALSE)</f>
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="G62" t="s">
         <v>1065</v>
@@ -6383,11 +6383,11 @@
         <v>10</v>
       </c>
       <c r="C63" t="s">
-        <v>60</v>
+        <v>878</v>
       </c>
       <c r="D63">
         <f>VLOOKUP(C63,$G$2:$H$1211,2,FALSE)</f>
-        <v>260</v>
+        <v>304</v>
       </c>
       <c r="G63" t="s">
         <v>123</v>
@@ -6404,11 +6404,11 @@
         <v>11</v>
       </c>
       <c r="C64" t="s">
-        <v>519</v>
+        <v>897</v>
       </c>
       <c r="D64">
         <f>VLOOKUP(C64,$G$2:$H$1211,2,FALSE)</f>
-        <v>178</v>
+        <v>312</v>
       </c>
       <c r="G64" t="s">
         <v>124</v>
@@ -6425,11 +6425,11 @@
         <v>12</v>
       </c>
       <c r="C65" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="D65">
         <f>VLOOKUP(C65,$G$2:$H$1211,2,FALSE)</f>
-        <v>23</v>
+        <v>380</v>
       </c>
       <c r="G65" t="s">
         <v>125</v>
@@ -6446,11 +6446,11 @@
         <v>13</v>
       </c>
       <c r="C66" t="s">
-        <v>66</v>
+        <v>868</v>
       </c>
       <c r="D66">
         <f>VLOOKUP(C66,$G$2:$H$1211,2,FALSE)</f>
-        <v>116</v>
+        <v>299</v>
       </c>
       <c r="G66" t="s">
         <v>15</v>
@@ -6467,11 +6467,11 @@
         <v>14</v>
       </c>
       <c r="C67" t="s">
-        <v>589</v>
+        <v>934</v>
       </c>
       <c r="D67">
         <f>VLOOKUP(C67,$G$2:$H$1211,2,FALSE)</f>
-        <v>198</v>
+        <v>326</v>
       </c>
       <c r="G67" t="s">
         <v>126</v>
@@ -6488,11 +6488,11 @@
         <v>15</v>
       </c>
       <c r="C68" t="s">
-        <v>269</v>
+        <v>705</v>
       </c>
       <c r="D68">
         <f>VLOOKUP(C68,$G$2:$H$1211,2,FALSE)</f>
-        <v>79</v>
+        <v>243</v>
       </c>
       <c r="G68" t="s">
         <v>127</v>
@@ -6509,11 +6509,11 @@
         <v>16</v>
       </c>
       <c r="C69" t="s">
-        <v>893</v>
+        <v>945</v>
       </c>
       <c r="D69">
         <f>VLOOKUP(C69,$G$2:$H$1211,2,FALSE)</f>
-        <v>310</v>
+        <v>332</v>
       </c>
       <c r="G69" t="s">
         <v>128</v>

--- a/L1/data/bracketology/espn_bracketology_2026.xlsx
+++ b/L1/data/bracketology/espn_bracketology_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ryanbrowder/Documents/Projects/marchMadness/L1/data/bracketology/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B76C8901-0F27-3B48-9875-8595A84AF9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{429F2E2D-5779-F743-BBAC-CBC54F23C0F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11820" yWindow="780" windowWidth="17060" windowHeight="17180" xr2:uid="{F87E21A2-B3CC-9145-B55E-990F91045160}"/>
   </bookViews>
@@ -4134,7 +4134,7 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D3">
         <v>180</v>
@@ -4190,10 +4190,10 @@
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="D7">
-        <v>142</v>
+        <v>374</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -4204,10 +4204,10 @@
         <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D8">
-        <v>177</v>
+        <v>355</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -4218,7 +4218,7 @@
         <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>986</v>
       </c>
       <c r="D9">
         <v>347</v>
@@ -4232,10 +4232,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="D10">
-        <v>331</v>
+        <v>132</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
@@ -4260,10 +4260,10 @@
         <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>60</v>
+        <v>799</v>
       </c>
       <c r="D12">
-        <v>260</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
@@ -4274,10 +4274,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D13">
-        <v>129</v>
+        <v>260</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
@@ -4288,10 +4288,10 @@
         <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="D14">
-        <v>23</v>
+        <v>380</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
@@ -4302,10 +4302,10 @@
         <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>16</v>
+        <v>868</v>
       </c>
       <c r="D15">
-        <v>337</v>
+        <v>299</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
@@ -4344,10 +4344,10 @@
         <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>186</v>
+        <v>893</v>
       </c>
       <c r="D18">
-        <v>45</v>
+        <v>310</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
@@ -4372,10 +4372,10 @@
         <v>2</v>
       </c>
       <c r="C20" t="s">
-        <v>56</v>
+        <v>1064</v>
       </c>
       <c r="D20">
-        <v>119</v>
+        <v>62</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
@@ -4386,10 +4386,10 @@
         <v>3</v>
       </c>
       <c r="C21" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="D21">
-        <v>199</v>
+        <v>248</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
@@ -4400,10 +4400,10 @@
         <v>4</v>
       </c>
       <c r="C22" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D22">
-        <v>138</v>
+        <v>356</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
@@ -4414,10 +4414,10 @@
         <v>5</v>
       </c>
       <c r="C23" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="D23">
-        <v>13</v>
+        <v>308</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
@@ -4428,10 +4428,10 @@
         <v>6</v>
       </c>
       <c r="C24" t="s">
-        <v>6</v>
+        <v>57</v>
       </c>
       <c r="D24">
-        <v>353</v>
+        <v>211</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
@@ -4442,10 +4442,10 @@
         <v>7</v>
       </c>
       <c r="C25" t="s">
-        <v>768</v>
+        <v>11</v>
       </c>
       <c r="D25">
-        <v>266</v>
+        <v>104</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
@@ -4456,10 +4456,10 @@
         <v>8</v>
       </c>
       <c r="C26" t="s">
-        <v>28</v>
+        <v>764</v>
       </c>
       <c r="D26">
-        <v>55</v>
+        <v>265</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
@@ -4470,10 +4470,10 @@
         <v>9</v>
       </c>
       <c r="C27" t="s">
-        <v>944</v>
+        <v>878</v>
       </c>
       <c r="D27">
-        <v>330</v>
+        <v>304</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
@@ -4484,10 +4484,10 @@
         <v>10</v>
       </c>
       <c r="C28" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="D28">
-        <v>229</v>
+        <v>196</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
@@ -4498,10 +4498,10 @@
         <v>11</v>
       </c>
       <c r="C29" t="s">
-        <v>519</v>
+        <v>993</v>
       </c>
       <c r="D29">
-        <v>178</v>
+        <v>350</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
@@ -4509,13 +4509,13 @@
         <v>20</v>
       </c>
       <c r="B30">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C30" t="s">
-        <v>826</v>
+        <v>43</v>
       </c>
       <c r="D30">
-        <v>284</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
@@ -4523,13 +4523,13 @@
         <v>20</v>
       </c>
       <c r="B31">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C31" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="D31">
-        <v>116</v>
+        <v>150</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
@@ -4537,13 +4537,13 @@
         <v>20</v>
       </c>
       <c r="B32">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C32" t="s">
-        <v>589</v>
+        <v>634</v>
       </c>
       <c r="D32">
-        <v>198</v>
+        <v>215</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
@@ -4551,13 +4551,13 @@
         <v>20</v>
       </c>
       <c r="B33">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C33" t="s">
-        <v>269</v>
+        <v>589</v>
       </c>
       <c r="D33">
-        <v>79</v>
+        <v>198</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
@@ -4565,13 +4565,13 @@
         <v>20</v>
       </c>
       <c r="B34">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C34" t="s">
-        <v>372</v>
+        <v>513</v>
       </c>
       <c r="D34">
-        <v>121</v>
+        <v>176</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
@@ -4582,24 +4582,24 @@
         <v>16</v>
       </c>
       <c r="C35" t="s">
-        <v>127</v>
+        <v>945</v>
       </c>
       <c r="D35">
-        <v>24</v>
+        <v>332</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B36">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C36" t="s">
-        <v>1064</v>
+        <v>432</v>
       </c>
       <c r="D36">
-        <v>62</v>
+        <v>143</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
@@ -4607,7 +4607,7 @@
         <v>37</v>
       </c>
       <c r="B37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C37" t="s">
         <v>58</v>
@@ -4621,13 +4621,13 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C38" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D38">
-        <v>248</v>
+        <v>119</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
@@ -4635,13 +4635,13 @@
         <v>37</v>
       </c>
       <c r="B39">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C39" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D39">
-        <v>356</v>
+        <v>199</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
@@ -4649,13 +4649,13 @@
         <v>37</v>
       </c>
       <c r="B40">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C40" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D40">
-        <v>308</v>
+        <v>138</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
@@ -4663,13 +4663,13 @@
         <v>37</v>
       </c>
       <c r="B41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C41" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="D41">
-        <v>159</v>
+        <v>13</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
@@ -4677,13 +4677,13 @@
         <v>37</v>
       </c>
       <c r="B42">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C42" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="D42">
-        <v>355</v>
+        <v>159</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
@@ -4691,13 +4691,13 @@
         <v>37</v>
       </c>
       <c r="B43">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C43" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="D43">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
@@ -4705,13 +4705,13 @@
         <v>37</v>
       </c>
       <c r="B44">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C44" t="s">
-        <v>10</v>
+        <v>62</v>
       </c>
       <c r="D44">
-        <v>132</v>
+        <v>177</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
@@ -4719,13 +4719,13 @@
         <v>37</v>
       </c>
       <c r="B45">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C45" t="s">
-        <v>899</v>
+        <v>669</v>
       </c>
       <c r="D45">
-        <v>313</v>
+        <v>229</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
@@ -4733,13 +4733,13 @@
         <v>37</v>
       </c>
       <c r="B46">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C46" t="s">
-        <v>799</v>
+        <v>897</v>
       </c>
       <c r="D46">
-        <v>274</v>
+        <v>312</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
@@ -4750,10 +4750,10 @@
         <v>11</v>
       </c>
       <c r="C47" t="s">
-        <v>602</v>
+        <v>944</v>
       </c>
       <c r="D47">
-        <v>204</v>
+        <v>330</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
@@ -4764,10 +4764,10 @@
         <v>12</v>
       </c>
       <c r="C48" t="s">
-        <v>50</v>
+        <v>826</v>
       </c>
       <c r="D48">
-        <v>150</v>
+        <v>284</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
@@ -4778,10 +4778,10 @@
         <v>13</v>
       </c>
       <c r="C49" t="s">
-        <v>156</v>
+        <v>16</v>
       </c>
       <c r="D49">
-        <v>36</v>
+        <v>337</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
@@ -4792,10 +4792,10 @@
         <v>14</v>
       </c>
       <c r="C50" t="s">
-        <v>634</v>
+        <v>269</v>
       </c>
       <c r="D50">
-        <v>215</v>
+        <v>79</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
@@ -4806,10 +4806,10 @@
         <v>15</v>
       </c>
       <c r="C51" t="s">
-        <v>513</v>
+        <v>186</v>
       </c>
       <c r="D51">
-        <v>176</v>
+        <v>45</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
@@ -4820,10 +4820,10 @@
         <v>16</v>
       </c>
       <c r="C52" t="s">
-        <v>893</v>
+        <v>372</v>
       </c>
       <c r="D52">
-        <v>310</v>
+        <v>121</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
@@ -4834,10 +4834,10 @@
         <v>16</v>
       </c>
       <c r="C53" t="s">
-        <v>432</v>
+        <v>127</v>
       </c>
       <c r="D53">
-        <v>143</v>
+        <v>24</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
@@ -4904,10 +4904,10 @@
         <v>5</v>
       </c>
       <c r="C58" t="s">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="D58">
-        <v>211</v>
+        <v>353</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
@@ -4918,10 +4918,10 @@
         <v>6</v>
       </c>
       <c r="C59" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="D59">
-        <v>374</v>
+        <v>142</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
@@ -4946,10 +4946,10 @@
         <v>8</v>
       </c>
       <c r="C61" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="D61">
-        <v>104</v>
+        <v>55</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
@@ -4960,10 +4960,10 @@
         <v>9</v>
       </c>
       <c r="C62" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="D62">
-        <v>196</v>
+        <v>331</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
@@ -4974,10 +4974,10 @@
         <v>10</v>
       </c>
       <c r="C63" t="s">
-        <v>878</v>
+        <v>899</v>
       </c>
       <c r="D63">
-        <v>304</v>
+        <v>313</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
@@ -4988,10 +4988,10 @@
         <v>11</v>
       </c>
       <c r="C64" t="s">
-        <v>897</v>
+        <v>519</v>
       </c>
       <c r="D64">
-        <v>312</v>
+        <v>178</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
@@ -5002,10 +5002,10 @@
         <v>12</v>
       </c>
       <c r="C65" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="D65">
-        <v>380</v>
+        <v>116</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
@@ -5016,10 +5016,10 @@
         <v>13</v>
       </c>
       <c r="C66" t="s">
-        <v>868</v>
+        <v>156</v>
       </c>
       <c r="D66">
-        <v>299</v>
+        <v>36</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
@@ -5044,10 +5044,10 @@
         <v>15</v>
       </c>
       <c r="C68" t="s">
-        <v>705</v>
+        <v>385</v>
       </c>
       <c r="D68">
-        <v>243</v>
+        <v>126</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
@@ -5058,10 +5058,10 @@
         <v>16</v>
       </c>
       <c r="C69" t="s">
-        <v>945</v>
+        <v>705</v>
       </c>
       <c r="D69">
-        <v>332</v>
+        <v>243</v>
       </c>
     </row>
   </sheetData>
@@ -5123,7 +5123,7 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D3">
         <f t="shared" ref="D3:D13" si="0">VLOOKUP(C3,$G$2:$H$1211,2,FALSE)</f>
@@ -5207,11 +5207,11 @@
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
-        <v>142</v>
+        <v>374</v>
       </c>
       <c r="G7" t="s">
         <v>76</v>
@@ -5228,11 +5228,11 @@
         <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
-        <v>177</v>
+        <v>355</v>
       </c>
       <c r="G8" t="s">
         <v>64</v>
@@ -5249,7 +5249,7 @@
         <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>986</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
@@ -5270,11 +5270,11 @@
         <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
-        <v>331</v>
+        <v>132</v>
       </c>
       <c r="G10" t="s">
         <v>23</v>
@@ -5312,11 +5312,11 @@
         <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>60</v>
+        <v>799</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
-        <v>260</v>
+        <v>274</v>
       </c>
       <c r="G12" t="s">
         <v>79</v>
@@ -5333,11 +5333,11 @@
         <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D13">
         <f t="shared" si="0"/>
-        <v>129</v>
+        <v>260</v>
       </c>
       <c r="G13" t="s">
         <v>80</v>
@@ -5354,11 +5354,11 @@
         <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="D14">
-        <f t="shared" ref="D14:D45" si="1">VLOOKUP(C14,$G$2:$H$1211,2,FALSE)</f>
-        <v>23</v>
+        <f t="shared" ref="D14:D29" si="1">VLOOKUP(C14,$G$2:$H$1211,2,FALSE)</f>
+        <v>380</v>
       </c>
       <c r="G14" t="s">
         <v>81</v>
@@ -5375,11 +5375,11 @@
         <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>16</v>
+        <v>868</v>
       </c>
       <c r="D15">
         <f t="shared" si="1"/>
-        <v>337</v>
+        <v>299</v>
       </c>
       <c r="G15" t="s">
         <v>82</v>
@@ -5438,11 +5438,11 @@
         <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>186</v>
+        <v>893</v>
       </c>
       <c r="D18">
         <f t="shared" si="1"/>
-        <v>45</v>
+        <v>310</v>
       </c>
       <c r="G18" t="s">
         <v>85</v>
@@ -5480,11 +5480,11 @@
         <v>2</v>
       </c>
       <c r="C20" t="s">
-        <v>56</v>
+        <v>1064</v>
       </c>
       <c r="D20">
         <f t="shared" si="1"/>
-        <v>119</v>
+        <v>62</v>
       </c>
       <c r="G20" t="s">
         <v>87</v>
@@ -5501,11 +5501,11 @@
         <v>3</v>
       </c>
       <c r="C21" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="D21">
         <f t="shared" si="1"/>
-        <v>199</v>
+        <v>248</v>
       </c>
       <c r="G21" t="s">
         <v>88</v>
@@ -5522,11 +5522,11 @@
         <v>4</v>
       </c>
       <c r="C22" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D22">
         <f t="shared" si="1"/>
-        <v>138</v>
+        <v>356</v>
       </c>
       <c r="G22" t="s">
         <v>89</v>
@@ -5543,11 +5543,11 @@
         <v>5</v>
       </c>
       <c r="C23" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="D23">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>308</v>
       </c>
       <c r="G23" t="s">
         <v>90</v>
@@ -5564,11 +5564,11 @@
         <v>6</v>
       </c>
       <c r="C24" t="s">
-        <v>6</v>
+        <v>57</v>
       </c>
       <c r="D24">
         <f t="shared" si="1"/>
-        <v>353</v>
+        <v>211</v>
       </c>
       <c r="G24" t="s">
         <v>91</v>
@@ -5585,11 +5585,11 @@
         <v>7</v>
       </c>
       <c r="C25" t="s">
-        <v>768</v>
+        <v>11</v>
       </c>
       <c r="D25">
         <f t="shared" si="1"/>
-        <v>266</v>
+        <v>104</v>
       </c>
       <c r="G25" t="s">
         <v>92</v>
@@ -5606,11 +5606,11 @@
         <v>8</v>
       </c>
       <c r="C26" t="s">
-        <v>28</v>
+        <v>764</v>
       </c>
       <c r="D26">
         <f t="shared" si="1"/>
-        <v>55</v>
+        <v>265</v>
       </c>
       <c r="G26" t="s">
         <v>93</v>
@@ -5627,11 +5627,11 @@
         <v>9</v>
       </c>
       <c r="C27" t="s">
-        <v>944</v>
+        <v>878</v>
       </c>
       <c r="D27">
         <f t="shared" si="1"/>
-        <v>330</v>
+        <v>304</v>
       </c>
       <c r="G27" t="s">
         <v>94</v>
@@ -5648,11 +5648,11 @@
         <v>10</v>
       </c>
       <c r="C28" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="D28">
         <f t="shared" si="1"/>
-        <v>229</v>
+        <v>196</v>
       </c>
       <c r="G28" t="s">
         <v>95</v>
@@ -5669,11 +5669,11 @@
         <v>11</v>
       </c>
       <c r="C29" t="s">
-        <v>519</v>
+        <v>993</v>
       </c>
       <c r="D29">
         <f t="shared" si="1"/>
-        <v>178</v>
+        <v>350</v>
       </c>
       <c r="G29" t="s">
         <v>96</v>
@@ -5687,14 +5687,14 @@
         <v>20</v>
       </c>
       <c r="B30">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C30" t="s">
-        <v>826</v>
+        <v>43</v>
       </c>
       <c r="D30">
-        <f>VLOOKUP(C30,$G$2:$H$1211,2,FALSE)</f>
-        <v>284</v>
+        <f t="shared" ref="D30" si="2">VLOOKUP(C30,$G$2:$H$1211,2,FALSE)</f>
+        <v>17</v>
       </c>
       <c r="G30" t="s">
         <v>97</v>
@@ -5708,14 +5708,14 @@
         <v>20</v>
       </c>
       <c r="B31">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C31" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="D31">
         <f>VLOOKUP(C31,$G$2:$H$1211,2,FALSE)</f>
-        <v>116</v>
+        <v>150</v>
       </c>
       <c r="G31" t="s">
         <v>98</v>
@@ -5729,14 +5729,14 @@
         <v>20</v>
       </c>
       <c r="B32">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C32" t="s">
-        <v>589</v>
+        <v>634</v>
       </c>
       <c r="D32">
         <f>VLOOKUP(C32,$G$2:$H$1211,2,FALSE)</f>
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="G32" t="s">
         <v>99</v>
@@ -5750,14 +5750,14 @@
         <v>20</v>
       </c>
       <c r="B33">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C33" t="s">
-        <v>269</v>
+        <v>589</v>
       </c>
       <c r="D33">
         <f>VLOOKUP(C33,$G$2:$H$1211,2,FALSE)</f>
-        <v>79</v>
+        <v>198</v>
       </c>
       <c r="G33" t="s">
         <v>54</v>
@@ -5771,14 +5771,14 @@
         <v>20</v>
       </c>
       <c r="B34">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C34" t="s">
-        <v>372</v>
+        <v>513</v>
       </c>
       <c r="D34">
         <f>VLOOKUP(C34,$G$2:$H$1211,2,FALSE)</f>
-        <v>121</v>
+        <v>176</v>
       </c>
       <c r="G34" t="s">
         <v>100</v>
@@ -5795,11 +5795,11 @@
         <v>16</v>
       </c>
       <c r="C35" t="s">
-        <v>127</v>
+        <v>945</v>
       </c>
       <c r="D35">
         <f>VLOOKUP(C35,$G$2:$H$1211,2,FALSE)</f>
-        <v>24</v>
+        <v>332</v>
       </c>
       <c r="G35" t="s">
         <v>101</v>
@@ -5810,17 +5810,17 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B36">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C36" t="s">
-        <v>1064</v>
+        <v>432</v>
       </c>
       <c r="D36">
         <f>VLOOKUP(C36,$G$2:$H$1211,2,FALSE)</f>
-        <v>62</v>
+        <v>143</v>
       </c>
       <c r="G36" t="s">
         <v>102</v>
@@ -5834,7 +5834,7 @@
         <v>37</v>
       </c>
       <c r="B37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C37" t="s">
         <v>58</v>
@@ -5855,14 +5855,14 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C38" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D38">
         <f>VLOOKUP(C38,$G$2:$H$1211,2,FALSE)</f>
-        <v>248</v>
+        <v>119</v>
       </c>
       <c r="G38" t="s">
         <v>104</v>
@@ -5876,14 +5876,14 @@
         <v>37</v>
       </c>
       <c r="B39">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C39" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D39">
         <f>VLOOKUP(C39,$G$2:$H$1211,2,FALSE)</f>
-        <v>356</v>
+        <v>199</v>
       </c>
       <c r="G39" t="s">
         <v>59</v>
@@ -5897,14 +5897,14 @@
         <v>37</v>
       </c>
       <c r="B40">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C40" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D40">
         <f>VLOOKUP(C40,$G$2:$H$1211,2,FALSE)</f>
-        <v>308</v>
+        <v>138</v>
       </c>
       <c r="G40" t="s">
         <v>105</v>
@@ -5918,14 +5918,14 @@
         <v>37</v>
       </c>
       <c r="B41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C41" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="D41">
         <f>VLOOKUP(C41,$G$2:$H$1211,2,FALSE)</f>
-        <v>159</v>
+        <v>13</v>
       </c>
       <c r="G41" t="s">
         <v>106</v>
@@ -5939,14 +5939,14 @@
         <v>37</v>
       </c>
       <c r="B42">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C42" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="D42">
         <f>VLOOKUP(C42,$G$2:$H$1211,2,FALSE)</f>
-        <v>355</v>
+        <v>159</v>
       </c>
       <c r="G42" t="s">
         <v>107</v>
@@ -5960,14 +5960,14 @@
         <v>37</v>
       </c>
       <c r="B43">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C43" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="D43">
         <f>VLOOKUP(C43,$G$2:$H$1211,2,FALSE)</f>
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="G43" t="s">
         <v>108</v>
@@ -5981,14 +5981,14 @@
         <v>37</v>
       </c>
       <c r="B44">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C44" t="s">
-        <v>10</v>
+        <v>62</v>
       </c>
       <c r="D44">
         <f>VLOOKUP(C44,$G$2:$H$1211,2,FALSE)</f>
-        <v>132</v>
+        <v>177</v>
       </c>
       <c r="G44" t="s">
         <v>109</v>
@@ -6002,14 +6002,14 @@
         <v>37</v>
       </c>
       <c r="B45">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C45" t="s">
-        <v>899</v>
+        <v>669</v>
       </c>
       <c r="D45">
         <f>VLOOKUP(C45,$G$2:$H$1211,2,FALSE)</f>
-        <v>313</v>
+        <v>229</v>
       </c>
       <c r="G45" t="s">
         <v>110</v>
@@ -6023,14 +6023,14 @@
         <v>37</v>
       </c>
       <c r="B46">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C46" t="s">
-        <v>799</v>
+        <v>897</v>
       </c>
       <c r="D46">
         <f>VLOOKUP(C46,$G$2:$H$1211,2,FALSE)</f>
-        <v>274</v>
+        <v>312</v>
       </c>
       <c r="G46" t="s">
         <v>111</v>
@@ -6047,11 +6047,11 @@
         <v>11</v>
       </c>
       <c r="C47" t="s">
-        <v>602</v>
+        <v>944</v>
       </c>
       <c r="D47">
         <f>VLOOKUP(C47,$G$2:$H$1211,2,FALSE)</f>
-        <v>204</v>
+        <v>330</v>
       </c>
       <c r="G47" t="s">
         <v>17</v>
@@ -6068,11 +6068,11 @@
         <v>12</v>
       </c>
       <c r="C48" t="s">
-        <v>50</v>
+        <v>826</v>
       </c>
       <c r="D48">
         <f>VLOOKUP(C48,$G$2:$H$1211,2,FALSE)</f>
-        <v>150</v>
+        <v>284</v>
       </c>
       <c r="G48" t="s">
         <v>112</v>
@@ -6089,11 +6089,11 @@
         <v>13</v>
       </c>
       <c r="C49" t="s">
-        <v>156</v>
+        <v>16</v>
       </c>
       <c r="D49">
         <f>VLOOKUP(C49,$G$2:$H$1211,2,FALSE)</f>
-        <v>36</v>
+        <v>337</v>
       </c>
       <c r="G49" t="s">
         <v>113</v>
@@ -6110,11 +6110,11 @@
         <v>14</v>
       </c>
       <c r="C50" t="s">
-        <v>634</v>
+        <v>269</v>
       </c>
       <c r="D50">
         <f>VLOOKUP(C50,$G$2:$H$1211,2,FALSE)</f>
-        <v>215</v>
+        <v>79</v>
       </c>
       <c r="G50" t="s">
         <v>114</v>
@@ -6131,11 +6131,11 @@
         <v>15</v>
       </c>
       <c r="C51" t="s">
-        <v>513</v>
+        <v>186</v>
       </c>
       <c r="D51">
         <f>VLOOKUP(C51,$G$2:$H$1211,2,FALSE)</f>
-        <v>176</v>
+        <v>45</v>
       </c>
       <c r="G51" t="s">
         <v>43</v>
@@ -6152,11 +6152,11 @@
         <v>16</v>
       </c>
       <c r="C52" t="s">
-        <v>893</v>
+        <v>372</v>
       </c>
       <c r="D52">
         <f>VLOOKUP(C52,$G$2:$H$1211,2,FALSE)</f>
-        <v>310</v>
+        <v>121</v>
       </c>
       <c r="G52" t="s">
         <v>115</v>
@@ -6173,11 +6173,11 @@
         <v>16</v>
       </c>
       <c r="C53" t="s">
-        <v>432</v>
+        <v>127</v>
       </c>
       <c r="D53">
         <f>VLOOKUP(C53,$G$2:$H$1211,2,FALSE)</f>
-        <v>143</v>
+        <v>24</v>
       </c>
       <c r="G53" t="s">
         <v>116</v>
@@ -6278,11 +6278,11 @@
         <v>5</v>
       </c>
       <c r="C58" t="s">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="D58">
         <f>VLOOKUP(C58,$G$2:$H$1211,2,FALSE)</f>
-        <v>211</v>
+        <v>353</v>
       </c>
       <c r="G58" t="s">
         <v>120</v>
@@ -6299,11 +6299,11 @@
         <v>6</v>
       </c>
       <c r="C59" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="D59">
         <f>VLOOKUP(C59,$G$2:$H$1211,2,FALSE)</f>
-        <v>374</v>
+        <v>142</v>
       </c>
       <c r="G59" t="s">
         <v>121</v>
@@ -6341,11 +6341,11 @@
         <v>8</v>
       </c>
       <c r="C61" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="D61">
         <f>VLOOKUP(C61,$G$2:$H$1211,2,FALSE)</f>
-        <v>104</v>
+        <v>55</v>
       </c>
       <c r="G61" t="s">
         <v>13</v>
@@ -6362,11 +6362,11 @@
         <v>9</v>
       </c>
       <c r="C62" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="D62">
         <f>VLOOKUP(C62,$G$2:$H$1211,2,FALSE)</f>
-        <v>196</v>
+        <v>331</v>
       </c>
       <c r="G62" t="s">
         <v>1065</v>
@@ -6383,11 +6383,11 @@
         <v>10</v>
       </c>
       <c r="C63" t="s">
-        <v>878</v>
+        <v>899</v>
       </c>
       <c r="D63">
         <f>VLOOKUP(C63,$G$2:$H$1211,2,FALSE)</f>
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="G63" t="s">
         <v>123</v>
@@ -6404,11 +6404,11 @@
         <v>11</v>
       </c>
       <c r="C64" t="s">
-        <v>897</v>
+        <v>519</v>
       </c>
       <c r="D64">
         <f>VLOOKUP(C64,$G$2:$H$1211,2,FALSE)</f>
-        <v>312</v>
+        <v>178</v>
       </c>
       <c r="G64" t="s">
         <v>124</v>
@@ -6425,11 +6425,11 @@
         <v>12</v>
       </c>
       <c r="C65" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="D65">
         <f>VLOOKUP(C65,$G$2:$H$1211,2,FALSE)</f>
-        <v>380</v>
+        <v>116</v>
       </c>
       <c r="G65" t="s">
         <v>125</v>
@@ -6446,11 +6446,11 @@
         <v>13</v>
       </c>
       <c r="C66" t="s">
-        <v>868</v>
+        <v>156</v>
       </c>
       <c r="D66">
         <f>VLOOKUP(C66,$G$2:$H$1211,2,FALSE)</f>
-        <v>299</v>
+        <v>36</v>
       </c>
       <c r="G66" t="s">
         <v>15</v>
@@ -6488,11 +6488,11 @@
         <v>15</v>
       </c>
       <c r="C68" t="s">
-        <v>705</v>
+        <v>385</v>
       </c>
       <c r="D68">
         <f>VLOOKUP(C68,$G$2:$H$1211,2,FALSE)</f>
-        <v>243</v>
+        <v>126</v>
       </c>
       <c r="G68" t="s">
         <v>127</v>
@@ -6509,11 +6509,11 @@
         <v>16</v>
       </c>
       <c r="C69" t="s">
-        <v>945</v>
+        <v>705</v>
       </c>
       <c r="D69">
         <f>VLOOKUP(C69,$G$2:$H$1211,2,FALSE)</f>
-        <v>332</v>
+        <v>243</v>
       </c>
       <c r="G69" t="s">
         <v>128</v>

--- a/L1/data/bracketology/espn_bracketology_2026.xlsx
+++ b/L1/data/bracketology/espn_bracketology_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ryanbrowder/Documents/Projects/marchMadness/L1/data/bracketology/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{429F2E2D-5779-F743-BBAC-CBC54F23C0F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E90D4E4-F5F5-8C48-B211-09E1244225D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11820" yWindow="780" windowWidth="17060" windowHeight="17180" xr2:uid="{F87E21A2-B3CC-9145-B55E-990F91045160}"/>
   </bookViews>
@@ -4162,10 +4162,10 @@
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>317</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -4176,10 +4176,10 @@
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>857</v>
+        <v>59</v>
       </c>
       <c r="D6">
-        <v>296</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -4218,10 +4218,10 @@
         <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>986</v>
+        <v>11</v>
       </c>
       <c r="D9">
-        <v>347</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -4232,10 +4232,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>10</v>
+        <v>669</v>
       </c>
       <c r="D10">
-        <v>132</v>
+        <v>229</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
@@ -4246,10 +4246,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>548</v>
+        <v>30</v>
       </c>
       <c r="D11">
-        <v>187</v>
+        <v>196</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
@@ -4288,10 +4288,10 @@
         <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>31</v>
+        <v>826</v>
       </c>
       <c r="D14">
-        <v>380</v>
+        <v>284</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
@@ -4316,10 +4316,10 @@
         <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>926</v>
+        <v>1052</v>
       </c>
       <c r="D16">
-        <v>321</v>
+        <v>377</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
@@ -4330,10 +4330,10 @@
         <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>1052</v>
+        <v>723</v>
       </c>
       <c r="D17">
-        <v>377</v>
+        <v>250</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
@@ -4344,10 +4344,10 @@
         <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>893</v>
+        <v>945</v>
       </c>
       <c r="D18">
-        <v>310</v>
+        <v>332</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
@@ -4400,10 +4400,10 @@
         <v>4</v>
       </c>
       <c r="C22" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D22">
-        <v>356</v>
+        <v>138</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
@@ -4414,10 +4414,10 @@
         <v>5</v>
       </c>
       <c r="C23" t="s">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="D23">
-        <v>308</v>
+        <v>353</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
@@ -4442,10 +4442,10 @@
         <v>7</v>
       </c>
       <c r="C25" t="s">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="D25">
-        <v>104</v>
+        <v>142</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
@@ -4456,10 +4456,10 @@
         <v>8</v>
       </c>
       <c r="C26" t="s">
-        <v>764</v>
+        <v>28</v>
       </c>
       <c r="D26">
-        <v>265</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
@@ -4470,10 +4470,10 @@
         <v>9</v>
       </c>
       <c r="C27" t="s">
-        <v>878</v>
+        <v>764</v>
       </c>
       <c r="D27">
-        <v>304</v>
+        <v>265</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
@@ -4484,10 +4484,10 @@
         <v>10</v>
       </c>
       <c r="C28" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D28">
-        <v>196</v>
+        <v>132</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
@@ -4498,10 +4498,10 @@
         <v>11</v>
       </c>
       <c r="C29" t="s">
-        <v>993</v>
+        <v>519</v>
       </c>
       <c r="D29">
-        <v>350</v>
+        <v>178</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
@@ -4509,13 +4509,13 @@
         <v>20</v>
       </c>
       <c r="B30">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C30" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="D30">
-        <v>17</v>
+        <v>116</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
@@ -4523,13 +4523,13 @@
         <v>20</v>
       </c>
       <c r="B31">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C31" t="s">
-        <v>50</v>
+        <v>634</v>
       </c>
       <c r="D31">
-        <v>150</v>
+        <v>215</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
@@ -4537,13 +4537,13 @@
         <v>20</v>
       </c>
       <c r="B32">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C32" t="s">
-        <v>634</v>
+        <v>363</v>
       </c>
       <c r="D32">
-        <v>215</v>
+        <v>117</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
@@ -4551,13 +4551,13 @@
         <v>20</v>
       </c>
       <c r="B33">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C33" t="s">
-        <v>589</v>
+        <v>513</v>
       </c>
       <c r="D33">
-        <v>198</v>
+        <v>176</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
@@ -4565,13 +4565,13 @@
         <v>20</v>
       </c>
       <c r="B34">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C34" t="s">
-        <v>513</v>
+        <v>127</v>
       </c>
       <c r="D34">
-        <v>176</v>
+        <v>24</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
@@ -4582,24 +4582,24 @@
         <v>16</v>
       </c>
       <c r="C35" t="s">
-        <v>945</v>
+        <v>445</v>
       </c>
       <c r="D35">
-        <v>332</v>
+        <v>149</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="B36">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C36" t="s">
-        <v>432</v>
+        <v>58</v>
       </c>
       <c r="D36">
-        <v>143</v>
+        <v>91</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
@@ -4607,13 +4607,13 @@
         <v>37</v>
       </c>
       <c r="B37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C37" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D37">
-        <v>91</v>
+        <v>119</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
@@ -4621,13 +4621,13 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C38" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="D38">
-        <v>119</v>
+        <v>199</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
@@ -4635,13 +4635,13 @@
         <v>37</v>
       </c>
       <c r="B39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C39" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D39">
-        <v>199</v>
+        <v>356</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
@@ -4649,13 +4649,13 @@
         <v>37</v>
       </c>
       <c r="B40">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C40" t="s">
-        <v>24</v>
+        <v>857</v>
       </c>
       <c r="D40">
-        <v>138</v>
+        <v>296</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
@@ -4663,13 +4663,13 @@
         <v>37</v>
       </c>
       <c r="B41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C41" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="D41">
-        <v>13</v>
+        <v>159</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
@@ -4677,13 +4677,13 @@
         <v>37</v>
       </c>
       <c r="B42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C42" t="s">
-        <v>41</v>
+        <v>768</v>
       </c>
       <c r="D42">
-        <v>159</v>
+        <v>266</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
@@ -4691,13 +4691,13 @@
         <v>37</v>
       </c>
       <c r="B43">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C43" t="s">
-        <v>768</v>
+        <v>986</v>
       </c>
       <c r="D43">
-        <v>266</v>
+        <v>347</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
@@ -4705,13 +4705,13 @@
         <v>37</v>
       </c>
       <c r="B44">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C44" t="s">
-        <v>62</v>
+        <v>878</v>
       </c>
       <c r="D44">
-        <v>177</v>
+        <v>304</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
@@ -4719,13 +4719,13 @@
         <v>37</v>
       </c>
       <c r="B45">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C45" t="s">
-        <v>669</v>
+        <v>548</v>
       </c>
       <c r="D45">
-        <v>229</v>
+        <v>187</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
@@ -4733,13 +4733,13 @@
         <v>37</v>
       </c>
       <c r="B46">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C46" t="s">
-        <v>897</v>
+        <v>993</v>
       </c>
       <c r="D46">
-        <v>312</v>
+        <v>350</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
@@ -4750,10 +4750,10 @@
         <v>11</v>
       </c>
       <c r="C47" t="s">
-        <v>944</v>
+        <v>43</v>
       </c>
       <c r="D47">
-        <v>330</v>
+        <v>17</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
@@ -4764,10 +4764,10 @@
         <v>12</v>
       </c>
       <c r="C48" t="s">
-        <v>826</v>
+        <v>31</v>
       </c>
       <c r="D48">
-        <v>284</v>
+        <v>380</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
@@ -4778,10 +4778,10 @@
         <v>13</v>
       </c>
       <c r="C49" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="D49">
-        <v>337</v>
+        <v>150</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
@@ -4792,10 +4792,10 @@
         <v>14</v>
       </c>
       <c r="C50" t="s">
-        <v>269</v>
+        <v>934</v>
       </c>
       <c r="D50">
-        <v>79</v>
+        <v>326</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
@@ -4806,10 +4806,10 @@
         <v>15</v>
       </c>
       <c r="C51" t="s">
-        <v>186</v>
+        <v>705</v>
       </c>
       <c r="D51">
-        <v>45</v>
+        <v>243</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
@@ -4820,10 +4820,10 @@
         <v>16</v>
       </c>
       <c r="C52" t="s">
-        <v>372</v>
+        <v>321</v>
       </c>
       <c r="D52">
-        <v>121</v>
+        <v>99</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
@@ -4834,10 +4834,10 @@
         <v>16</v>
       </c>
       <c r="C53" t="s">
-        <v>127</v>
+        <v>372</v>
       </c>
       <c r="D53">
-        <v>24</v>
+        <v>121</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
@@ -4876,10 +4876,10 @@
         <v>3</v>
       </c>
       <c r="C56" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D56">
-        <v>108</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
@@ -4890,10 +4890,10 @@
         <v>4</v>
       </c>
       <c r="C57" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="D57">
-        <v>317</v>
+        <v>108</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
@@ -4904,10 +4904,10 @@
         <v>5</v>
       </c>
       <c r="C58" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="D58">
-        <v>353</v>
+        <v>308</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
@@ -4918,10 +4918,10 @@
         <v>6</v>
       </c>
       <c r="C59" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="D59">
-        <v>142</v>
+        <v>19</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
@@ -4932,10 +4932,10 @@
         <v>7</v>
       </c>
       <c r="C60" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="D60">
-        <v>19</v>
+        <v>177</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
@@ -4946,10 +4946,10 @@
         <v>8</v>
       </c>
       <c r="C61" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="D61">
-        <v>55</v>
+        <v>331</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
@@ -4960,10 +4960,10 @@
         <v>9</v>
       </c>
       <c r="C62" t="s">
-        <v>45</v>
+        <v>899</v>
       </c>
       <c r="D62">
-        <v>331</v>
+        <v>313</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
@@ -4974,10 +4974,10 @@
         <v>10</v>
       </c>
       <c r="C63" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="D63">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
@@ -4988,10 +4988,10 @@
         <v>11</v>
       </c>
       <c r="C64" t="s">
-        <v>519</v>
+        <v>944</v>
       </c>
       <c r="D64">
-        <v>178</v>
+        <v>330</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
@@ -5002,10 +5002,10 @@
         <v>12</v>
       </c>
       <c r="C65" t="s">
-        <v>66</v>
+        <v>650</v>
       </c>
       <c r="D65">
-        <v>116</v>
+        <v>222</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
@@ -5016,10 +5016,10 @@
         <v>13</v>
       </c>
       <c r="C66" t="s">
-        <v>156</v>
+        <v>32</v>
       </c>
       <c r="D66">
-        <v>36</v>
+        <v>349</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
@@ -5030,10 +5030,10 @@
         <v>14</v>
       </c>
       <c r="C67" t="s">
-        <v>934</v>
+        <v>926</v>
       </c>
       <c r="D67">
-        <v>326</v>
+        <v>321</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
@@ -5044,10 +5044,10 @@
         <v>15</v>
       </c>
       <c r="C68" t="s">
-        <v>385</v>
+        <v>893</v>
       </c>
       <c r="D68">
-        <v>126</v>
+        <v>310</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
@@ -5058,10 +5058,10 @@
         <v>16</v>
       </c>
       <c r="C69" t="s">
-        <v>705</v>
+        <v>432</v>
       </c>
       <c r="D69">
-        <v>243</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -5165,11 +5165,11 @@
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>317</v>
       </c>
       <c r="G5" t="s">
         <v>74</v>
@@ -5186,11 +5186,11 @@
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>857</v>
+        <v>59</v>
       </c>
       <c r="D6">
         <f t="shared" si="0"/>
-        <v>296</v>
+        <v>13</v>
       </c>
       <c r="G6" t="s">
         <v>75</v>
@@ -5249,11 +5249,11 @@
         <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>986</v>
+        <v>11</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
-        <v>347</v>
+        <v>104</v>
       </c>
       <c r="G9" t="s">
         <v>77</v>
@@ -5270,11 +5270,11 @@
         <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>10</v>
+        <v>669</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
-        <v>132</v>
+        <v>229</v>
       </c>
       <c r="G10" t="s">
         <v>23</v>
@@ -5291,11 +5291,11 @@
         <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>548</v>
+        <v>30</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="G11" t="s">
         <v>78</v>
@@ -5315,7 +5315,7 @@
         <v>799</v>
       </c>
       <c r="D12">
-        <f t="shared" si="0"/>
+        <f>VLOOKUP(C12,$G$2:$H$1211,2,FALSE)</f>
         <v>274</v>
       </c>
       <c r="G12" t="s">
@@ -5336,7 +5336,7 @@
         <v>60</v>
       </c>
       <c r="D13">
-        <f t="shared" si="0"/>
+        <f>VLOOKUP(C13,$G$2:$H$1211,2,FALSE)</f>
         <v>260</v>
       </c>
       <c r="G13" t="s">
@@ -5354,11 +5354,11 @@
         <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>31</v>
+        <v>826</v>
       </c>
       <c r="D14">
         <f t="shared" ref="D14:D29" si="1">VLOOKUP(C14,$G$2:$H$1211,2,FALSE)</f>
-        <v>380</v>
+        <v>284</v>
       </c>
       <c r="G14" t="s">
         <v>81</v>
@@ -5396,11 +5396,11 @@
         <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>926</v>
+        <v>1052</v>
       </c>
       <c r="D16">
         <f t="shared" si="1"/>
-        <v>321</v>
+        <v>377</v>
       </c>
       <c r="G16" t="s">
         <v>83</v>
@@ -5417,11 +5417,11 @@
         <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>1052</v>
+        <v>723</v>
       </c>
       <c r="D17">
         <f t="shared" si="1"/>
-        <v>377</v>
+        <v>250</v>
       </c>
       <c r="G17" t="s">
         <v>84</v>
@@ -5438,11 +5438,11 @@
         <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>893</v>
+        <v>945</v>
       </c>
       <c r="D18">
         <f t="shared" si="1"/>
-        <v>310</v>
+        <v>332</v>
       </c>
       <c r="G18" t="s">
         <v>85</v>
@@ -5522,11 +5522,11 @@
         <v>4</v>
       </c>
       <c r="C22" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D22">
         <f t="shared" si="1"/>
-        <v>356</v>
+        <v>138</v>
       </c>
       <c r="G22" t="s">
         <v>89</v>
@@ -5543,11 +5543,11 @@
         <v>5</v>
       </c>
       <c r="C23" t="s">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="D23">
         <f t="shared" si="1"/>
-        <v>308</v>
+        <v>353</v>
       </c>
       <c r="G23" t="s">
         <v>90</v>
@@ -5585,11 +5585,11 @@
         <v>7</v>
       </c>
       <c r="C25" t="s">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="D25">
         <f t="shared" si="1"/>
-        <v>104</v>
+        <v>142</v>
       </c>
       <c r="G25" t="s">
         <v>92</v>
@@ -5606,11 +5606,11 @@
         <v>8</v>
       </c>
       <c r="C26" t="s">
-        <v>764</v>
+        <v>28</v>
       </c>
       <c r="D26">
         <f t="shared" si="1"/>
-        <v>265</v>
+        <v>55</v>
       </c>
       <c r="G26" t="s">
         <v>93</v>
@@ -5627,11 +5627,11 @@
         <v>9</v>
       </c>
       <c r="C27" t="s">
-        <v>878</v>
+        <v>764</v>
       </c>
       <c r="D27">
         <f t="shared" si="1"/>
-        <v>304</v>
+        <v>265</v>
       </c>
       <c r="G27" t="s">
         <v>94</v>
@@ -5648,11 +5648,11 @@
         <v>10</v>
       </c>
       <c r="C28" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D28">
         <f t="shared" si="1"/>
-        <v>196</v>
+        <v>132</v>
       </c>
       <c r="G28" t="s">
         <v>95</v>
@@ -5669,11 +5669,11 @@
         <v>11</v>
       </c>
       <c r="C29" t="s">
-        <v>993</v>
+        <v>519</v>
       </c>
       <c r="D29">
         <f t="shared" si="1"/>
-        <v>350</v>
+        <v>178</v>
       </c>
       <c r="G29" t="s">
         <v>96</v>
@@ -5687,14 +5687,14 @@
         <v>20</v>
       </c>
       <c r="B30">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C30" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="D30">
-        <f t="shared" ref="D30" si="2">VLOOKUP(C30,$G$2:$H$1211,2,FALSE)</f>
-        <v>17</v>
+        <f t="shared" ref="D30:D68" si="2">VLOOKUP(C30,$G$2:$H$1211,2,FALSE)</f>
+        <v>116</v>
       </c>
       <c r="G30" t="s">
         <v>97</v>
@@ -5708,14 +5708,14 @@
         <v>20</v>
       </c>
       <c r="B31">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C31" t="s">
-        <v>50</v>
+        <v>634</v>
       </c>
       <c r="D31">
-        <f>VLOOKUP(C31,$G$2:$H$1211,2,FALSE)</f>
-        <v>150</v>
+        <f t="shared" si="2"/>
+        <v>215</v>
       </c>
       <c r="G31" t="s">
         <v>98</v>
@@ -5729,14 +5729,14 @@
         <v>20</v>
       </c>
       <c r="B32">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C32" t="s">
-        <v>634</v>
+        <v>363</v>
       </c>
       <c r="D32">
-        <f>VLOOKUP(C32,$G$2:$H$1211,2,FALSE)</f>
-        <v>215</v>
+        <f t="shared" si="2"/>
+        <v>117</v>
       </c>
       <c r="G32" t="s">
         <v>99</v>
@@ -5750,14 +5750,14 @@
         <v>20</v>
       </c>
       <c r="B33">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C33" t="s">
-        <v>589</v>
+        <v>513</v>
       </c>
       <c r="D33">
-        <f>VLOOKUP(C33,$G$2:$H$1211,2,FALSE)</f>
-        <v>198</v>
+        <f t="shared" si="2"/>
+        <v>176</v>
       </c>
       <c r="G33" t="s">
         <v>54</v>
@@ -5771,14 +5771,14 @@
         <v>20</v>
       </c>
       <c r="B34">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C34" t="s">
-        <v>513</v>
+        <v>127</v>
       </c>
       <c r="D34">
-        <f>VLOOKUP(C34,$G$2:$H$1211,2,FALSE)</f>
-        <v>176</v>
+        <f t="shared" si="2"/>
+        <v>24</v>
       </c>
       <c r="G34" t="s">
         <v>100</v>
@@ -5795,11 +5795,11 @@
         <v>16</v>
       </c>
       <c r="C35" t="s">
-        <v>945</v>
+        <v>445</v>
       </c>
       <c r="D35">
-        <f>VLOOKUP(C35,$G$2:$H$1211,2,FALSE)</f>
-        <v>332</v>
+        <f t="shared" si="2"/>
+        <v>149</v>
       </c>
       <c r="G35" t="s">
         <v>101</v>
@@ -5810,17 +5810,17 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="B36">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C36" t="s">
-        <v>432</v>
+        <v>58</v>
       </c>
       <c r="D36">
-        <f>VLOOKUP(C36,$G$2:$H$1211,2,FALSE)</f>
-        <v>143</v>
+        <f t="shared" si="2"/>
+        <v>91</v>
       </c>
       <c r="G36" t="s">
         <v>102</v>
@@ -5834,14 +5834,14 @@
         <v>37</v>
       </c>
       <c r="B37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C37" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D37">
-        <f>VLOOKUP(C37,$G$2:$H$1211,2,FALSE)</f>
-        <v>91</v>
+        <f t="shared" si="2"/>
+        <v>119</v>
       </c>
       <c r="G37" t="s">
         <v>103</v>
@@ -5855,14 +5855,14 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C38" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="D38">
-        <f>VLOOKUP(C38,$G$2:$H$1211,2,FALSE)</f>
-        <v>119</v>
+        <f t="shared" si="2"/>
+        <v>199</v>
       </c>
       <c r="G38" t="s">
         <v>104</v>
@@ -5876,14 +5876,14 @@
         <v>37</v>
       </c>
       <c r="B39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C39" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D39">
-        <f>VLOOKUP(C39,$G$2:$H$1211,2,FALSE)</f>
-        <v>199</v>
+        <f t="shared" si="2"/>
+        <v>356</v>
       </c>
       <c r="G39" t="s">
         <v>59</v>
@@ -5897,14 +5897,14 @@
         <v>37</v>
       </c>
       <c r="B40">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C40" t="s">
-        <v>24</v>
+        <v>857</v>
       </c>
       <c r="D40">
-        <f>VLOOKUP(C40,$G$2:$H$1211,2,FALSE)</f>
-        <v>138</v>
+        <f t="shared" si="2"/>
+        <v>296</v>
       </c>
       <c r="G40" t="s">
         <v>105</v>
@@ -5918,14 +5918,14 @@
         <v>37</v>
       </c>
       <c r="B41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C41" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="D41">
-        <f>VLOOKUP(C41,$G$2:$H$1211,2,FALSE)</f>
-        <v>13</v>
+        <f t="shared" si="2"/>
+        <v>159</v>
       </c>
       <c r="G41" t="s">
         <v>106</v>
@@ -5939,14 +5939,14 @@
         <v>37</v>
       </c>
       <c r="B42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C42" t="s">
-        <v>41</v>
+        <v>768</v>
       </c>
       <c r="D42">
-        <f>VLOOKUP(C42,$G$2:$H$1211,2,FALSE)</f>
-        <v>159</v>
+        <f t="shared" si="2"/>
+        <v>266</v>
       </c>
       <c r="G42" t="s">
         <v>107</v>
@@ -5960,14 +5960,14 @@
         <v>37</v>
       </c>
       <c r="B43">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C43" t="s">
-        <v>768</v>
+        <v>986</v>
       </c>
       <c r="D43">
-        <f>VLOOKUP(C43,$G$2:$H$1211,2,FALSE)</f>
-        <v>266</v>
+        <f t="shared" si="2"/>
+        <v>347</v>
       </c>
       <c r="G43" t="s">
         <v>108</v>
@@ -5981,14 +5981,14 @@
         <v>37</v>
       </c>
       <c r="B44">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C44" t="s">
-        <v>62</v>
+        <v>878</v>
       </c>
       <c r="D44">
-        <f>VLOOKUP(C44,$G$2:$H$1211,2,FALSE)</f>
-        <v>177</v>
+        <f t="shared" si="2"/>
+        <v>304</v>
       </c>
       <c r="G44" t="s">
         <v>109</v>
@@ -6002,14 +6002,14 @@
         <v>37</v>
       </c>
       <c r="B45">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C45" t="s">
-        <v>669</v>
+        <v>548</v>
       </c>
       <c r="D45">
-        <f>VLOOKUP(C45,$G$2:$H$1211,2,FALSE)</f>
-        <v>229</v>
+        <f t="shared" si="2"/>
+        <v>187</v>
       </c>
       <c r="G45" t="s">
         <v>110</v>
@@ -6023,14 +6023,14 @@
         <v>37</v>
       </c>
       <c r="B46">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C46" t="s">
-        <v>897</v>
+        <v>993</v>
       </c>
       <c r="D46">
-        <f>VLOOKUP(C46,$G$2:$H$1211,2,FALSE)</f>
-        <v>312</v>
+        <f t="shared" si="2"/>
+        <v>350</v>
       </c>
       <c r="G46" t="s">
         <v>111</v>
@@ -6047,11 +6047,11 @@
         <v>11</v>
       </c>
       <c r="C47" t="s">
-        <v>944</v>
+        <v>43</v>
       </c>
       <c r="D47">
-        <f>VLOOKUP(C47,$G$2:$H$1211,2,FALSE)</f>
-        <v>330</v>
+        <f t="shared" si="2"/>
+        <v>17</v>
       </c>
       <c r="G47" t="s">
         <v>17</v>
@@ -6068,11 +6068,11 @@
         <v>12</v>
       </c>
       <c r="C48" t="s">
-        <v>826</v>
+        <v>31</v>
       </c>
       <c r="D48">
         <f>VLOOKUP(C48,$G$2:$H$1211,2,FALSE)</f>
-        <v>284</v>
+        <v>380</v>
       </c>
       <c r="G48" t="s">
         <v>112</v>
@@ -6089,11 +6089,11 @@
         <v>13</v>
       </c>
       <c r="C49" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="D49">
         <f>VLOOKUP(C49,$G$2:$H$1211,2,FALSE)</f>
-        <v>337</v>
+        <v>150</v>
       </c>
       <c r="G49" t="s">
         <v>113</v>
@@ -6110,11 +6110,11 @@
         <v>14</v>
       </c>
       <c r="C50" t="s">
-        <v>269</v>
+        <v>934</v>
       </c>
       <c r="D50">
         <f>VLOOKUP(C50,$G$2:$H$1211,2,FALSE)</f>
-        <v>79</v>
+        <v>326</v>
       </c>
       <c r="G50" t="s">
         <v>114</v>
@@ -6131,11 +6131,11 @@
         <v>15</v>
       </c>
       <c r="C51" t="s">
-        <v>186</v>
+        <v>705</v>
       </c>
       <c r="D51">
         <f>VLOOKUP(C51,$G$2:$H$1211,2,FALSE)</f>
-        <v>45</v>
+        <v>243</v>
       </c>
       <c r="G51" t="s">
         <v>43</v>
@@ -6152,11 +6152,11 @@
         <v>16</v>
       </c>
       <c r="C52" t="s">
-        <v>372</v>
+        <v>321</v>
       </c>
       <c r="D52">
         <f>VLOOKUP(C52,$G$2:$H$1211,2,FALSE)</f>
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="G52" t="s">
         <v>115</v>
@@ -6173,11 +6173,11 @@
         <v>16</v>
       </c>
       <c r="C53" t="s">
-        <v>127</v>
+        <v>372</v>
       </c>
       <c r="D53">
         <f>VLOOKUP(C53,$G$2:$H$1211,2,FALSE)</f>
-        <v>24</v>
+        <v>121</v>
       </c>
       <c r="G53" t="s">
         <v>116</v>
@@ -6236,11 +6236,11 @@
         <v>3</v>
       </c>
       <c r="C56" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D56">
         <f>VLOOKUP(C56,$G$2:$H$1211,2,FALSE)</f>
-        <v>108</v>
+        <v>4</v>
       </c>
       <c r="G56" t="s">
         <v>118</v>
@@ -6257,11 +6257,11 @@
         <v>4</v>
       </c>
       <c r="C57" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="D57">
         <f>VLOOKUP(C57,$G$2:$H$1211,2,FALSE)</f>
-        <v>317</v>
+        <v>108</v>
       </c>
       <c r="G57" t="s">
         <v>119</v>
@@ -6278,11 +6278,11 @@
         <v>5</v>
       </c>
       <c r="C58" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="D58">
         <f>VLOOKUP(C58,$G$2:$H$1211,2,FALSE)</f>
-        <v>353</v>
+        <v>308</v>
       </c>
       <c r="G58" t="s">
         <v>120</v>
@@ -6299,11 +6299,11 @@
         <v>6</v>
       </c>
       <c r="C59" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="D59">
         <f>VLOOKUP(C59,$G$2:$H$1211,2,FALSE)</f>
-        <v>142</v>
+        <v>19</v>
       </c>
       <c r="G59" t="s">
         <v>121</v>
@@ -6320,11 +6320,11 @@
         <v>7</v>
       </c>
       <c r="C60" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="D60">
         <f>VLOOKUP(C60,$G$2:$H$1211,2,FALSE)</f>
-        <v>19</v>
+        <v>177</v>
       </c>
       <c r="G60" t="s">
         <v>122</v>
@@ -6341,11 +6341,11 @@
         <v>8</v>
       </c>
       <c r="C61" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="D61">
         <f>VLOOKUP(C61,$G$2:$H$1211,2,FALSE)</f>
-        <v>55</v>
+        <v>331</v>
       </c>
       <c r="G61" t="s">
         <v>13</v>
@@ -6362,11 +6362,11 @@
         <v>9</v>
       </c>
       <c r="C62" t="s">
-        <v>45</v>
+        <v>899</v>
       </c>
       <c r="D62">
         <f>VLOOKUP(C62,$G$2:$H$1211,2,FALSE)</f>
-        <v>331</v>
+        <v>313</v>
       </c>
       <c r="G62" t="s">
         <v>1065</v>
@@ -6383,11 +6383,11 @@
         <v>10</v>
       </c>
       <c r="C63" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="D63">
         <f>VLOOKUP(C63,$G$2:$H$1211,2,FALSE)</f>
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G63" t="s">
         <v>123</v>
@@ -6404,11 +6404,11 @@
         <v>11</v>
       </c>
       <c r="C64" t="s">
-        <v>519</v>
+        <v>944</v>
       </c>
       <c r="D64">
         <f>VLOOKUP(C64,$G$2:$H$1211,2,FALSE)</f>
-        <v>178</v>
+        <v>330</v>
       </c>
       <c r="G64" t="s">
         <v>124</v>
@@ -6425,11 +6425,11 @@
         <v>12</v>
       </c>
       <c r="C65" t="s">
-        <v>66</v>
+        <v>650</v>
       </c>
       <c r="D65">
         <f>VLOOKUP(C65,$G$2:$H$1211,2,FALSE)</f>
-        <v>116</v>
+        <v>222</v>
       </c>
       <c r="G65" t="s">
         <v>125</v>
@@ -6446,11 +6446,11 @@
         <v>13</v>
       </c>
       <c r="C66" t="s">
-        <v>156</v>
+        <v>32</v>
       </c>
       <c r="D66">
         <f>VLOOKUP(C66,$G$2:$H$1211,2,FALSE)</f>
-        <v>36</v>
+        <v>349</v>
       </c>
       <c r="G66" t="s">
         <v>15</v>
@@ -6467,11 +6467,11 @@
         <v>14</v>
       </c>
       <c r="C67" t="s">
-        <v>934</v>
+        <v>926</v>
       </c>
       <c r="D67">
         <f>VLOOKUP(C67,$G$2:$H$1211,2,FALSE)</f>
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="G67" t="s">
         <v>126</v>
@@ -6488,11 +6488,11 @@
         <v>15</v>
       </c>
       <c r="C68" t="s">
-        <v>385</v>
+        <v>893</v>
       </c>
       <c r="D68">
         <f>VLOOKUP(C68,$G$2:$H$1211,2,FALSE)</f>
-        <v>126</v>
+        <v>310</v>
       </c>
       <c r="G68" t="s">
         <v>127</v>
@@ -6509,11 +6509,11 @@
         <v>16</v>
       </c>
       <c r="C69" t="s">
-        <v>705</v>
+        <v>432</v>
       </c>
       <c r="D69">
         <f>VLOOKUP(C69,$G$2:$H$1211,2,FALSE)</f>
-        <v>243</v>
+        <v>143</v>
       </c>
       <c r="G69" t="s">
         <v>128</v>

--- a/L1/data/bracketology/espn_bracketology_2026.xlsx
+++ b/L1/data/bracketology/espn_bracketology_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ryanbrowder/Documents/Projects/marchMadness/L1/data/bracketology/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E90D4E4-F5F5-8C48-B211-09E1244225D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8756C3B9-1CF7-8345-9F47-E51D84E3B5D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11820" yWindow="780" windowWidth="17060" windowHeight="17180" xr2:uid="{F87E21A2-B3CC-9145-B55E-990F91045160}"/>
+    <workbookView xWindow="12520" yWindow="780" windowWidth="16360" windowHeight="17180" xr2:uid="{F87E21A2-B3CC-9145-B55E-990F91045160}"/>
   </bookViews>
   <sheets>
     <sheet name="espn_bracketology_2026" sheetId="1" r:id="rId1"/>
@@ -4148,10 +4148,10 @@
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>401</v>
+        <v>23</v>
       </c>
       <c r="D4">
-        <v>133</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -4162,10 +4162,10 @@
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="D5">
-        <v>317</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -4176,10 +4176,10 @@
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="D6">
-        <v>13</v>
+        <v>308</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -4190,10 +4190,10 @@
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="D7">
-        <v>374</v>
+        <v>211</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -4218,10 +4218,10 @@
         <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="D9">
-        <v>104</v>
+        <v>177</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -4232,10 +4232,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>669</v>
+        <v>10</v>
       </c>
       <c r="D10">
-        <v>229</v>
+        <v>132</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
@@ -4246,10 +4246,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>944</v>
       </c>
       <c r="D11">
-        <v>196</v>
+        <v>330</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
@@ -4260,10 +4260,10 @@
         <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>799</v>
+        <v>519</v>
       </c>
       <c r="D12">
-        <v>274</v>
+        <v>178</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
@@ -4271,13 +4271,13 @@
         <v>3</v>
       </c>
       <c r="B13">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>60</v>
+        <v>650</v>
       </c>
       <c r="D13">
-        <v>260</v>
+        <v>222</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
@@ -4285,13 +4285,13 @@
         <v>3</v>
       </c>
       <c r="B14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>826</v>
+        <v>780</v>
       </c>
       <c r="D14">
-        <v>284</v>
+        <v>268</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
@@ -4299,13 +4299,13 @@
         <v>3</v>
       </c>
       <c r="B15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="s">
-        <v>868</v>
+        <v>926</v>
       </c>
       <c r="D15">
-        <v>299</v>
+        <v>321</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
@@ -4313,13 +4313,13 @@
         <v>3</v>
       </c>
       <c r="B16">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>1052</v>
+        <v>723</v>
       </c>
       <c r="D16">
-        <v>377</v>
+        <v>250</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
@@ -4327,27 +4327,27 @@
         <v>3</v>
       </c>
       <c r="B17">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C17" t="s">
-        <v>723</v>
+        <v>51</v>
       </c>
       <c r="D17">
-        <v>250</v>
+        <v>278</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B18">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>945</v>
+        <v>21</v>
       </c>
       <c r="D18">
-        <v>332</v>
+        <v>179</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
@@ -4355,13 +4355,13 @@
         <v>20</v>
       </c>
       <c r="B19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="s">
-        <v>21</v>
+        <v>1064</v>
       </c>
       <c r="D19">
-        <v>179</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
@@ -4369,13 +4369,13 @@
         <v>20</v>
       </c>
       <c r="B20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C20" t="s">
-        <v>1064</v>
+        <v>401</v>
       </c>
       <c r="D20">
-        <v>62</v>
+        <v>133</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
@@ -4383,13 +4383,13 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C21" t="s">
-        <v>55</v>
+        <v>8</v>
       </c>
       <c r="D21">
-        <v>248</v>
+        <v>317</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
@@ -4397,13 +4397,13 @@
         <v>20</v>
       </c>
       <c r="B22">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C22" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="D22">
-        <v>138</v>
+        <v>353</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
@@ -4411,13 +4411,13 @@
         <v>20</v>
       </c>
       <c r="B23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C23" t="s">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="D23">
-        <v>353</v>
+        <v>159</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
@@ -4425,13 +4425,13 @@
         <v>20</v>
       </c>
       <c r="B24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C24" t="s">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="D24">
-        <v>211</v>
+        <v>104</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
@@ -4439,13 +4439,13 @@
         <v>20</v>
       </c>
       <c r="B25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C25" t="s">
-        <v>46</v>
+        <v>986</v>
       </c>
       <c r="D25">
-        <v>142</v>
+        <v>347</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
@@ -4453,7 +4453,7 @@
         <v>20</v>
       </c>
       <c r="B26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C26" t="s">
         <v>28</v>
@@ -4467,13 +4467,13 @@
         <v>20</v>
       </c>
       <c r="B27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C27" t="s">
-        <v>764</v>
+        <v>799</v>
       </c>
       <c r="D27">
-        <v>265</v>
+        <v>274</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
@@ -4481,13 +4481,13 @@
         <v>20</v>
       </c>
       <c r="B28">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C28" t="s">
-        <v>10</v>
+        <v>548</v>
       </c>
       <c r="D28">
-        <v>132</v>
+        <v>187</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
@@ -4498,10 +4498,10 @@
         <v>11</v>
       </c>
       <c r="C29" t="s">
-        <v>519</v>
+        <v>993</v>
       </c>
       <c r="D29">
-        <v>178</v>
+        <v>350</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
@@ -4526,10 +4526,10 @@
         <v>13</v>
       </c>
       <c r="C31" t="s">
-        <v>634</v>
+        <v>32</v>
       </c>
       <c r="D31">
-        <v>215</v>
+        <v>349</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
@@ -4540,10 +4540,10 @@
         <v>14</v>
       </c>
       <c r="C32" t="s">
-        <v>363</v>
+        <v>634</v>
       </c>
       <c r="D32">
-        <v>117</v>
+        <v>215</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
@@ -4554,10 +4554,10 @@
         <v>15</v>
       </c>
       <c r="C33" t="s">
-        <v>513</v>
+        <v>945</v>
       </c>
       <c r="D33">
-        <v>176</v>
+        <v>332</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
@@ -4568,10 +4568,10 @@
         <v>16</v>
       </c>
       <c r="C34" t="s">
-        <v>127</v>
+        <v>372</v>
       </c>
       <c r="D34">
-        <v>24</v>
+        <v>121</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
@@ -4582,10 +4582,10 @@
         <v>16</v>
       </c>
       <c r="C35" t="s">
-        <v>445</v>
+        <v>377</v>
       </c>
       <c r="D35">
-        <v>149</v>
+        <v>123</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
@@ -4638,10 +4638,10 @@
         <v>4</v>
       </c>
       <c r="C39" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="D39">
-        <v>356</v>
+        <v>248</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
@@ -4666,10 +4666,10 @@
         <v>6</v>
       </c>
       <c r="C41" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D41">
-        <v>159</v>
+        <v>19</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
@@ -4694,10 +4694,10 @@
         <v>8</v>
       </c>
       <c r="C43" t="s">
-        <v>986</v>
+        <v>878</v>
       </c>
       <c r="D43">
-        <v>347</v>
+        <v>304</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
@@ -4708,10 +4708,10 @@
         <v>9</v>
       </c>
       <c r="C44" t="s">
-        <v>878</v>
+        <v>669</v>
       </c>
       <c r="D44">
-        <v>304</v>
+        <v>229</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
@@ -4722,10 +4722,10 @@
         <v>10</v>
       </c>
       <c r="C45" t="s">
-        <v>548</v>
+        <v>30</v>
       </c>
       <c r="D45">
-        <v>187</v>
+        <v>196</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
@@ -4736,10 +4736,10 @@
         <v>11</v>
       </c>
       <c r="C46" t="s">
-        <v>993</v>
+        <v>60</v>
       </c>
       <c r="D46">
-        <v>350</v>
+        <v>260</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
@@ -4764,10 +4764,10 @@
         <v>12</v>
       </c>
       <c r="C48" t="s">
-        <v>31</v>
+        <v>826</v>
       </c>
       <c r="D48">
-        <v>380</v>
+        <v>284</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
@@ -4778,10 +4778,10 @@
         <v>13</v>
       </c>
       <c r="C49" t="s">
-        <v>50</v>
+        <v>363</v>
       </c>
       <c r="D49">
-        <v>150</v>
+        <v>117</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
@@ -4792,10 +4792,10 @@
         <v>14</v>
       </c>
       <c r="C50" t="s">
-        <v>934</v>
+        <v>1052</v>
       </c>
       <c r="D50">
-        <v>326</v>
+        <v>377</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
@@ -4806,10 +4806,10 @@
         <v>15</v>
       </c>
       <c r="C51" t="s">
-        <v>705</v>
+        <v>321</v>
       </c>
       <c r="D51">
-        <v>243</v>
+        <v>99</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
@@ -4820,10 +4820,10 @@
         <v>16</v>
       </c>
       <c r="C52" t="s">
-        <v>321</v>
+        <v>839</v>
       </c>
       <c r="D52">
-        <v>99</v>
+        <v>288</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
@@ -4834,10 +4834,10 @@
         <v>16</v>
       </c>
       <c r="C53" t="s">
-        <v>372</v>
+        <v>445</v>
       </c>
       <c r="D53">
-        <v>121</v>
+        <v>149</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
@@ -4876,10 +4876,10 @@
         <v>3</v>
       </c>
       <c r="C56" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D56">
-        <v>4</v>
+        <v>108</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
@@ -4890,10 +4890,10 @@
         <v>4</v>
       </c>
       <c r="C57" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D57">
-        <v>108</v>
+        <v>356</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
@@ -4904,10 +4904,10 @@
         <v>5</v>
       </c>
       <c r="C58" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="D58">
-        <v>308</v>
+        <v>13</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
@@ -4918,10 +4918,10 @@
         <v>6</v>
       </c>
       <c r="C59" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="D59">
-        <v>19</v>
+        <v>374</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
@@ -4932,10 +4932,10 @@
         <v>7</v>
       </c>
       <c r="C60" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="D60">
-        <v>177</v>
+        <v>142</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
@@ -4974,10 +4974,10 @@
         <v>10</v>
       </c>
       <c r="C63" t="s">
-        <v>897</v>
+        <v>14</v>
       </c>
       <c r="D63">
-        <v>312</v>
+        <v>265</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
@@ -4988,10 +4988,10 @@
         <v>11</v>
       </c>
       <c r="C64" t="s">
-        <v>944</v>
+        <v>897</v>
       </c>
       <c r="D64">
-        <v>330</v>
+        <v>312</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
@@ -5002,10 +5002,10 @@
         <v>12</v>
       </c>
       <c r="C65" t="s">
-        <v>650</v>
+        <v>31</v>
       </c>
       <c r="D65">
-        <v>222</v>
+        <v>380</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
@@ -5016,10 +5016,10 @@
         <v>13</v>
       </c>
       <c r="C66" t="s">
-        <v>32</v>
+        <v>501</v>
       </c>
       <c r="D66">
-        <v>349</v>
+        <v>171</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
@@ -5030,10 +5030,10 @@
         <v>14</v>
       </c>
       <c r="C67" t="s">
-        <v>926</v>
+        <v>934</v>
       </c>
       <c r="D67">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
@@ -5126,7 +5126,7 @@
         <v>522</v>
       </c>
       <c r="D3">
-        <f t="shared" ref="D3:D13" si="0">VLOOKUP(C3,$G$2:$H$1211,2,FALSE)</f>
+        <f t="shared" ref="D3:D11" si="0">VLOOKUP(C3,$G$2:$H$1211,2,FALSE)</f>
         <v>180</v>
       </c>
       <c r="G3" t="s">
@@ -5144,11 +5144,11 @@
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>401</v>
+        <v>23</v>
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
-        <v>133</v>
+        <v>4</v>
       </c>
       <c r="G4" t="s">
         <v>73</v>
@@ -5165,11 +5165,11 @@
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
-        <v>317</v>
+        <v>138</v>
       </c>
       <c r="G5" t="s">
         <v>74</v>
@@ -5186,11 +5186,11 @@
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="D6">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>308</v>
       </c>
       <c r="G6" t="s">
         <v>75</v>
@@ -5207,11 +5207,11 @@
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
-        <v>374</v>
+        <v>211</v>
       </c>
       <c r="G7" t="s">
         <v>76</v>
@@ -5249,11 +5249,11 @@
         <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
-        <v>104</v>
+        <v>177</v>
       </c>
       <c r="G9" t="s">
         <v>77</v>
@@ -5270,11 +5270,11 @@
         <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>669</v>
+        <v>10</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
-        <v>229</v>
+        <v>132</v>
       </c>
       <c r="G10" t="s">
         <v>23</v>
@@ -5291,11 +5291,11 @@
         <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>944</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
-        <v>196</v>
+        <v>330</v>
       </c>
       <c r="G11" t="s">
         <v>78</v>
@@ -5312,11 +5312,11 @@
         <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>799</v>
+        <v>519</v>
       </c>
       <c r="D12">
         <f>VLOOKUP(C12,$G$2:$H$1211,2,FALSE)</f>
-        <v>274</v>
+        <v>178</v>
       </c>
       <c r="G12" t="s">
         <v>79</v>
@@ -5330,14 +5330,14 @@
         <v>3</v>
       </c>
       <c r="B13">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>60</v>
+        <v>650</v>
       </c>
       <c r="D13">
-        <f>VLOOKUP(C13,$G$2:$H$1211,2,FALSE)</f>
-        <v>260</v>
+        <f t="shared" ref="D13:D28" si="1">VLOOKUP(C13,$G$2:$H$1211,2,FALSE)</f>
+        <v>222</v>
       </c>
       <c r="G13" t="s">
         <v>80</v>
@@ -5351,14 +5351,14 @@
         <v>3</v>
       </c>
       <c r="B14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>826</v>
+        <v>780</v>
       </c>
       <c r="D14">
-        <f t="shared" ref="D14:D29" si="1">VLOOKUP(C14,$G$2:$H$1211,2,FALSE)</f>
-        <v>284</v>
+        <f t="shared" si="1"/>
+        <v>268</v>
       </c>
       <c r="G14" t="s">
         <v>81</v>
@@ -5372,14 +5372,14 @@
         <v>3</v>
       </c>
       <c r="B15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="s">
-        <v>868</v>
+        <v>926</v>
       </c>
       <c r="D15">
         <f t="shared" si="1"/>
-        <v>299</v>
+        <v>321</v>
       </c>
       <c r="G15" t="s">
         <v>82</v>
@@ -5393,14 +5393,14 @@
         <v>3</v>
       </c>
       <c r="B16">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>1052</v>
+        <v>723</v>
       </c>
       <c r="D16">
         <f t="shared" si="1"/>
-        <v>377</v>
+        <v>250</v>
       </c>
       <c r="G16" t="s">
         <v>83</v>
@@ -5414,14 +5414,14 @@
         <v>3</v>
       </c>
       <c r="B17">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C17" t="s">
-        <v>723</v>
+        <v>51</v>
       </c>
       <c r="D17">
         <f t="shared" si="1"/>
-        <v>250</v>
+        <v>278</v>
       </c>
       <c r="G17" t="s">
         <v>84</v>
@@ -5432,17 +5432,17 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B18">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>945</v>
+        <v>21</v>
       </c>
       <c r="D18">
         <f t="shared" si="1"/>
-        <v>332</v>
+        <v>179</v>
       </c>
       <c r="G18" t="s">
         <v>85</v>
@@ -5456,14 +5456,14 @@
         <v>20</v>
       </c>
       <c r="B19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="s">
-        <v>21</v>
+        <v>1064</v>
       </c>
       <c r="D19">
         <f t="shared" si="1"/>
-        <v>179</v>
+        <v>62</v>
       </c>
       <c r="G19" t="s">
         <v>86</v>
@@ -5477,14 +5477,14 @@
         <v>20</v>
       </c>
       <c r="B20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C20" t="s">
-        <v>1064</v>
+        <v>401</v>
       </c>
       <c r="D20">
         <f t="shared" si="1"/>
-        <v>62</v>
+        <v>133</v>
       </c>
       <c r="G20" t="s">
         <v>87</v>
@@ -5498,14 +5498,14 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C21" t="s">
-        <v>55</v>
+        <v>8</v>
       </c>
       <c r="D21">
         <f t="shared" si="1"/>
-        <v>248</v>
+        <v>317</v>
       </c>
       <c r="G21" t="s">
         <v>88</v>
@@ -5519,14 +5519,14 @@
         <v>20</v>
       </c>
       <c r="B22">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C22" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="D22">
         <f t="shared" si="1"/>
-        <v>138</v>
+        <v>353</v>
       </c>
       <c r="G22" t="s">
         <v>89</v>
@@ -5540,14 +5540,14 @@
         <v>20</v>
       </c>
       <c r="B23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C23" t="s">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="D23">
         <f t="shared" si="1"/>
-        <v>353</v>
+        <v>159</v>
       </c>
       <c r="G23" t="s">
         <v>90</v>
@@ -5561,14 +5561,14 @@
         <v>20</v>
       </c>
       <c r="B24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C24" t="s">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="D24">
         <f t="shared" si="1"/>
-        <v>211</v>
+        <v>104</v>
       </c>
       <c r="G24" t="s">
         <v>91</v>
@@ -5582,14 +5582,14 @@
         <v>20</v>
       </c>
       <c r="B25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C25" t="s">
-        <v>46</v>
+        <v>986</v>
       </c>
       <c r="D25">
         <f t="shared" si="1"/>
-        <v>142</v>
+        <v>347</v>
       </c>
       <c r="G25" t="s">
         <v>92</v>
@@ -5603,7 +5603,7 @@
         <v>20</v>
       </c>
       <c r="B26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C26" t="s">
         <v>28</v>
@@ -5624,14 +5624,14 @@
         <v>20</v>
       </c>
       <c r="B27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C27" t="s">
-        <v>764</v>
+        <v>799</v>
       </c>
       <c r="D27">
         <f t="shared" si="1"/>
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="G27" t="s">
         <v>94</v>
@@ -5645,14 +5645,14 @@
         <v>20</v>
       </c>
       <c r="B28">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C28" t="s">
-        <v>10</v>
+        <v>548</v>
       </c>
       <c r="D28">
         <f t="shared" si="1"/>
-        <v>132</v>
+        <v>187</v>
       </c>
       <c r="G28" t="s">
         <v>95</v>
@@ -5669,11 +5669,11 @@
         <v>11</v>
       </c>
       <c r="C29" t="s">
-        <v>519</v>
+        <v>993</v>
       </c>
       <c r="D29">
-        <f t="shared" si="1"/>
-        <v>178</v>
+        <f t="shared" ref="D29" si="2">VLOOKUP(C29,$G$2:$H$1211,2,FALSE)</f>
+        <v>350</v>
       </c>
       <c r="G29" t="s">
         <v>96</v>
@@ -5693,7 +5693,7 @@
         <v>66</v>
       </c>
       <c r="D30">
-        <f t="shared" ref="D30:D68" si="2">VLOOKUP(C30,$G$2:$H$1211,2,FALSE)</f>
+        <f t="shared" ref="D30:D47" si="3">VLOOKUP(C30,$G$2:$H$1211,2,FALSE)</f>
         <v>116</v>
       </c>
       <c r="G30" t="s">
@@ -5711,11 +5711,11 @@
         <v>13</v>
       </c>
       <c r="C31" t="s">
-        <v>634</v>
+        <v>32</v>
       </c>
       <c r="D31">
-        <f t="shared" si="2"/>
-        <v>215</v>
+        <f t="shared" si="3"/>
+        <v>349</v>
       </c>
       <c r="G31" t="s">
         <v>98</v>
@@ -5732,11 +5732,11 @@
         <v>14</v>
       </c>
       <c r="C32" t="s">
-        <v>363</v>
+        <v>634</v>
       </c>
       <c r="D32">
-        <f t="shared" si="2"/>
-        <v>117</v>
+        <f t="shared" si="3"/>
+        <v>215</v>
       </c>
       <c r="G32" t="s">
         <v>99</v>
@@ -5753,11 +5753,11 @@
         <v>15</v>
       </c>
       <c r="C33" t="s">
-        <v>513</v>
+        <v>945</v>
       </c>
       <c r="D33">
-        <f t="shared" si="2"/>
-        <v>176</v>
+        <f t="shared" si="3"/>
+        <v>332</v>
       </c>
       <c r="G33" t="s">
         <v>54</v>
@@ -5774,11 +5774,11 @@
         <v>16</v>
       </c>
       <c r="C34" t="s">
-        <v>127</v>
+        <v>372</v>
       </c>
       <c r="D34">
-        <f t="shared" si="2"/>
-        <v>24</v>
+        <f t="shared" si="3"/>
+        <v>121</v>
       </c>
       <c r="G34" t="s">
         <v>100</v>
@@ -5795,11 +5795,11 @@
         <v>16</v>
       </c>
       <c r="C35" t="s">
-        <v>445</v>
+        <v>377</v>
       </c>
       <c r="D35">
-        <f t="shared" si="2"/>
-        <v>149</v>
+        <f t="shared" si="3"/>
+        <v>123</v>
       </c>
       <c r="G35" t="s">
         <v>101</v>
@@ -5819,7 +5819,7 @@
         <v>58</v>
       </c>
       <c r="D36">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>91</v>
       </c>
       <c r="G36" t="s">
@@ -5840,7 +5840,7 @@
         <v>56</v>
       </c>
       <c r="D37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>119</v>
       </c>
       <c r="G37" t="s">
@@ -5861,7 +5861,7 @@
         <v>27</v>
       </c>
       <c r="D38">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>199</v>
       </c>
       <c r="G38" t="s">
@@ -5879,11 +5879,11 @@
         <v>4</v>
       </c>
       <c r="C39" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="D39">
-        <f t="shared" si="2"/>
-        <v>356</v>
+        <f t="shared" si="3"/>
+        <v>248</v>
       </c>
       <c r="G39" t="s">
         <v>59</v>
@@ -5903,7 +5903,7 @@
         <v>857</v>
       </c>
       <c r="D40">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>296</v>
       </c>
       <c r="G40" t="s">
@@ -5921,11 +5921,11 @@
         <v>6</v>
       </c>
       <c r="C41" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D41">
-        <f t="shared" si="2"/>
-        <v>159</v>
+        <f t="shared" si="3"/>
+        <v>19</v>
       </c>
       <c r="G41" t="s">
         <v>106</v>
@@ -5945,7 +5945,7 @@
         <v>768</v>
       </c>
       <c r="D42">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>266</v>
       </c>
       <c r="G42" t="s">
@@ -5963,11 +5963,11 @@
         <v>8</v>
       </c>
       <c r="C43" t="s">
-        <v>986</v>
+        <v>878</v>
       </c>
       <c r="D43">
-        <f t="shared" si="2"/>
-        <v>347</v>
+        <f t="shared" si="3"/>
+        <v>304</v>
       </c>
       <c r="G43" t="s">
         <v>108</v>
@@ -5984,11 +5984,11 @@
         <v>9</v>
       </c>
       <c r="C44" t="s">
-        <v>878</v>
+        <v>669</v>
       </c>
       <c r="D44">
-        <f t="shared" si="2"/>
-        <v>304</v>
+        <f t="shared" si="3"/>
+        <v>229</v>
       </c>
       <c r="G44" t="s">
         <v>109</v>
@@ -6005,11 +6005,11 @@
         <v>10</v>
       </c>
       <c r="C45" t="s">
-        <v>548</v>
+        <v>30</v>
       </c>
       <c r="D45">
-        <f t="shared" si="2"/>
-        <v>187</v>
+        <f t="shared" si="3"/>
+        <v>196</v>
       </c>
       <c r="G45" t="s">
         <v>110</v>
@@ -6026,11 +6026,11 @@
         <v>11</v>
       </c>
       <c r="C46" t="s">
-        <v>993</v>
+        <v>60</v>
       </c>
       <c r="D46">
-        <f t="shared" si="2"/>
-        <v>350</v>
+        <f t="shared" si="3"/>
+        <v>260</v>
       </c>
       <c r="G46" t="s">
         <v>111</v>
@@ -6050,7 +6050,7 @@
         <v>43</v>
       </c>
       <c r="D47">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="G47" t="s">
@@ -6068,11 +6068,11 @@
         <v>12</v>
       </c>
       <c r="C48" t="s">
-        <v>31</v>
+        <v>826</v>
       </c>
       <c r="D48">
-        <f>VLOOKUP(C48,$G$2:$H$1211,2,FALSE)</f>
-        <v>380</v>
+        <f t="shared" ref="D48:D69" si="4">VLOOKUP(C48,$G$2:$H$1211,2,FALSE)</f>
+        <v>284</v>
       </c>
       <c r="G48" t="s">
         <v>112</v>
@@ -6089,11 +6089,11 @@
         <v>13</v>
       </c>
       <c r="C49" t="s">
-        <v>50</v>
+        <v>363</v>
       </c>
       <c r="D49">
-        <f>VLOOKUP(C49,$G$2:$H$1211,2,FALSE)</f>
-        <v>150</v>
+        <f t="shared" si="4"/>
+        <v>117</v>
       </c>
       <c r="G49" t="s">
         <v>113</v>
@@ -6110,11 +6110,11 @@
         <v>14</v>
       </c>
       <c r="C50" t="s">
-        <v>934</v>
+        <v>1052</v>
       </c>
       <c r="D50">
-        <f>VLOOKUP(C50,$G$2:$H$1211,2,FALSE)</f>
-        <v>326</v>
+        <f t="shared" si="4"/>
+        <v>377</v>
       </c>
       <c r="G50" t="s">
         <v>114</v>
@@ -6131,11 +6131,11 @@
         <v>15</v>
       </c>
       <c r="C51" t="s">
-        <v>705</v>
+        <v>321</v>
       </c>
       <c r="D51">
-        <f>VLOOKUP(C51,$G$2:$H$1211,2,FALSE)</f>
-        <v>243</v>
+        <f t="shared" si="4"/>
+        <v>99</v>
       </c>
       <c r="G51" t="s">
         <v>43</v>
@@ -6152,11 +6152,11 @@
         <v>16</v>
       </c>
       <c r="C52" t="s">
-        <v>321</v>
+        <v>839</v>
       </c>
       <c r="D52">
-        <f>VLOOKUP(C52,$G$2:$H$1211,2,FALSE)</f>
-        <v>99</v>
+        <f t="shared" si="4"/>
+        <v>288</v>
       </c>
       <c r="G52" t="s">
         <v>115</v>
@@ -6173,11 +6173,11 @@
         <v>16</v>
       </c>
       <c r="C53" t="s">
-        <v>372</v>
+        <v>445</v>
       </c>
       <c r="D53">
-        <f>VLOOKUP(C53,$G$2:$H$1211,2,FALSE)</f>
-        <v>121</v>
+        <f t="shared" si="4"/>
+        <v>149</v>
       </c>
       <c r="G53" t="s">
         <v>116</v>
@@ -6197,7 +6197,7 @@
         <v>54</v>
       </c>
       <c r="D54">
-        <f>VLOOKUP(C54,$G$2:$H$1211,2,FALSE)</f>
+        <f t="shared" si="4"/>
         <v>11</v>
       </c>
       <c r="G54" t="s">
@@ -6218,7 +6218,7 @@
         <v>7</v>
       </c>
       <c r="D55">
-        <f>VLOOKUP(C55,$G$2:$H$1211,2,FALSE)</f>
+        <f t="shared" si="4"/>
         <v>125</v>
       </c>
       <c r="G55" t="s">
@@ -6236,11 +6236,11 @@
         <v>3</v>
       </c>
       <c r="C56" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D56">
-        <f>VLOOKUP(C56,$G$2:$H$1211,2,FALSE)</f>
-        <v>4</v>
+        <f t="shared" si="4"/>
+        <v>108</v>
       </c>
       <c r="G56" t="s">
         <v>118</v>
@@ -6257,11 +6257,11 @@
         <v>4</v>
       </c>
       <c r="C57" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D57">
-        <f>VLOOKUP(C57,$G$2:$H$1211,2,FALSE)</f>
-        <v>108</v>
+        <f t="shared" si="4"/>
+        <v>356</v>
       </c>
       <c r="G57" t="s">
         <v>119</v>
@@ -6278,11 +6278,11 @@
         <v>5</v>
       </c>
       <c r="C58" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="D58">
-        <f>VLOOKUP(C58,$G$2:$H$1211,2,FALSE)</f>
-        <v>308</v>
+        <f t="shared" si="4"/>
+        <v>13</v>
       </c>
       <c r="G58" t="s">
         <v>120</v>
@@ -6299,11 +6299,11 @@
         <v>6</v>
       </c>
       <c r="C59" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="D59">
-        <f>VLOOKUP(C59,$G$2:$H$1211,2,FALSE)</f>
-        <v>19</v>
+        <f t="shared" si="4"/>
+        <v>374</v>
       </c>
       <c r="G59" t="s">
         <v>121</v>
@@ -6320,11 +6320,11 @@
         <v>7</v>
       </c>
       <c r="C60" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="D60">
-        <f>VLOOKUP(C60,$G$2:$H$1211,2,FALSE)</f>
-        <v>177</v>
+        <f t="shared" si="4"/>
+        <v>142</v>
       </c>
       <c r="G60" t="s">
         <v>122</v>
@@ -6344,7 +6344,7 @@
         <v>45</v>
       </c>
       <c r="D61">
-        <f>VLOOKUP(C61,$G$2:$H$1211,2,FALSE)</f>
+        <f t="shared" si="4"/>
         <v>331</v>
       </c>
       <c r="G61" t="s">
@@ -6365,7 +6365,7 @@
         <v>899</v>
       </c>
       <c r="D62">
-        <f>VLOOKUP(C62,$G$2:$H$1211,2,FALSE)</f>
+        <f t="shared" si="4"/>
         <v>313</v>
       </c>
       <c r="G62" t="s">
@@ -6383,11 +6383,11 @@
         <v>10</v>
       </c>
       <c r="C63" t="s">
-        <v>897</v>
+        <v>14</v>
       </c>
       <c r="D63">
-        <f>VLOOKUP(C63,$G$2:$H$1211,2,FALSE)</f>
-        <v>312</v>
+        <f t="shared" si="4"/>
+        <v>265</v>
       </c>
       <c r="G63" t="s">
         <v>123</v>
@@ -6404,11 +6404,11 @@
         <v>11</v>
       </c>
       <c r="C64" t="s">
-        <v>944</v>
+        <v>897</v>
       </c>
       <c r="D64">
-        <f>VLOOKUP(C64,$G$2:$H$1211,2,FALSE)</f>
-        <v>330</v>
+        <f t="shared" si="4"/>
+        <v>312</v>
       </c>
       <c r="G64" t="s">
         <v>124</v>
@@ -6425,11 +6425,11 @@
         <v>12</v>
       </c>
       <c r="C65" t="s">
-        <v>650</v>
+        <v>31</v>
       </c>
       <c r="D65">
-        <f>VLOOKUP(C65,$G$2:$H$1211,2,FALSE)</f>
-        <v>222</v>
+        <f t="shared" si="4"/>
+        <v>380</v>
       </c>
       <c r="G65" t="s">
         <v>125</v>
@@ -6446,11 +6446,11 @@
         <v>13</v>
       </c>
       <c r="C66" t="s">
-        <v>32</v>
+        <v>501</v>
       </c>
       <c r="D66">
-        <f>VLOOKUP(C66,$G$2:$H$1211,2,FALSE)</f>
-        <v>349</v>
+        <f t="shared" si="4"/>
+        <v>171</v>
       </c>
       <c r="G66" t="s">
         <v>15</v>
@@ -6467,11 +6467,11 @@
         <v>14</v>
       </c>
       <c r="C67" t="s">
-        <v>926</v>
+        <v>934</v>
       </c>
       <c r="D67">
-        <f>VLOOKUP(C67,$G$2:$H$1211,2,FALSE)</f>
-        <v>321</v>
+        <f t="shared" si="4"/>
+        <v>326</v>
       </c>
       <c r="G67" t="s">
         <v>126</v>
@@ -6491,7 +6491,7 @@
         <v>893</v>
       </c>
       <c r="D68">
-        <f>VLOOKUP(C68,$G$2:$H$1211,2,FALSE)</f>
+        <f t="shared" si="4"/>
         <v>310</v>
       </c>
       <c r="G68" t="s">
@@ -6512,7 +6512,7 @@
         <v>432</v>
       </c>
       <c r="D69">
-        <f>VLOOKUP(C69,$G$2:$H$1211,2,FALSE)</f>
+        <f t="shared" si="4"/>
         <v>143</v>
       </c>
       <c r="G69" t="s">
